--- a/skills/tax/rsu/template_rsu.xlsx
+++ b/skills/tax/rsu/template_rsu.xlsx
@@ -933,7 +933,7 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="89" t="inlineStr">
         <is>
-          <t>Vesting of RSUs (Acquisition of Nu Holdings LTD shares)</t>
+          <t>Vesting of RSUs (acquisition of shares)</t>
         </is>
       </c>
       <c r="C6" s="86" t="n"/>

--- a/skills/tax/rsu/template_rsu.xlsx
+++ b/skills/tax/rsu/template_rsu.xlsx
@@ -216,7 +216,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -449,6 +449,9 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -933,7 +936,7 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="89" t="inlineStr">
         <is>
-          <t>Vesting of RSUs (acquisition of shares)</t>
+          <t>Vesting of RSUs — totals by release date (auto-computed from the per-grant detail below)</t>
         </is>
       </c>
       <c r="C6" s="86" t="n"/>
@@ -965,7 +968,7 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>release_date</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -1027,9 +1030,13 @@
           <t>Vesting</t>
         </is>
       </c>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="15" t="n">
-        <v>10.63</v>
+      <c r="D8" s="11">
+        <f>SUMIFS($E$30:$E$45,$B$30:$B$45,B8)</f>
+        <v/>
+      </c>
+      <c r="E8" s="15">
+        <f>IFERROR(INDEX($F$30:$F$45,MATCH(B8,$B$30:$B$45,0)),0)</f>
+        <v/>
       </c>
       <c r="F8" s="17">
         <f t="array" ref="F8">IFERROR(XLOOKUP(B8,aux_ptax_historical_data!B:B,aux_ptax_historical_data!E:E),"")</f>
@@ -1072,9 +1079,13 @@
           <t>Vesting</t>
         </is>
       </c>
-      <c r="D9" s="11" t="n"/>
-      <c r="E9" s="15" t="n">
-        <v>10.43</v>
+      <c r="D9" s="11">
+        <f>SUMIFS($E$30:$E$45,$B$30:$B$45,B9)</f>
+        <v/>
+      </c>
+      <c r="E9" s="15">
+        <f>IFERROR(INDEX($F$30:$F$45,MATCH(B9,$B$30:$B$45,0)),0)</f>
+        <v/>
       </c>
       <c r="F9" s="17">
         <f t="array" ref="F9">IFERROR(XLOOKUP(B9,aux_ptax_historical_data!B:B,aux_ptax_historical_data!E:E),"")</f>
@@ -1117,9 +1128,13 @@
           <t>Vesting</t>
         </is>
       </c>
-      <c r="D10" s="11" t="n"/>
-      <c r="E10" s="15" t="n">
-        <v>13.64</v>
+      <c r="D10" s="11">
+        <f>SUMIFS($E$30:$E$45,$B$30:$B$45,B10)</f>
+        <v/>
+      </c>
+      <c r="E10" s="15">
+        <f>IFERROR(INDEX($F$30:$F$45,MATCH(B10,$B$30:$B$45,0)),0)</f>
+        <v/>
       </c>
       <c r="F10" s="17">
         <f t="array" ref="F10">IFERROR(XLOOKUP(B10,aux_ptax_historical_data!B:B,aux_ptax_historical_data!E:E),"")</f>
@@ -1162,9 +1177,13 @@
           <t>Vesting</t>
         </is>
       </c>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="15" t="n">
-        <v>15.19</v>
+      <c r="D11" s="11">
+        <f>SUMIFS($E$30:$E$45,$B$30:$B$45,B11)</f>
+        <v/>
+      </c>
+      <c r="E11" s="15">
+        <f>IFERROR(INDEX($F$30:$F$45,MATCH(B11,$B$30:$B$45,0)),0)</f>
+        <v/>
       </c>
       <c r="F11" s="17">
         <f t="array" ref="F11">IFERROR(XLOOKUP(B11,aux_ptax_historical_data!B:B,aux_ptax_historical_data!E:E),"")</f>
@@ -1813,7 +1832,11 @@
     </row>
     <row r="28" ht="12.75" customHeight="1" s="85">
       <c r="A28" s="1" t="n"/>
-      <c r="B28" s="1" t="n"/>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>Vesting detail — enter one row per grant (release_date, award_date, award_number, net quantity, closing price)</t>
+        </is>
+      </c>
       <c r="C28" s="1" t="n"/>
       <c r="D28" s="1" t="n"/>
       <c r="E28" s="1" t="n"/>
@@ -1841,11 +1864,31 @@
     </row>
     <row r="29" ht="12.75" customHeight="1" s="85">
       <c r="A29" s="1" t="n"/>
-      <c r="B29" s="1" t="n"/>
-      <c r="C29" s="1" t="n"/>
-      <c r="D29" s="1" t="n"/>
-      <c r="E29" s="1" t="n"/>
-      <c r="F29" s="1" t="n"/>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>release_date</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="inlineStr">
+        <is>
+          <t>award_date</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="inlineStr">
+        <is>
+          <t>award_number</t>
+        </is>
+      </c>
+      <c r="E29" s="1" t="inlineStr">
+        <is>
+          <t>net_quantity</t>
+        </is>
+      </c>
+      <c r="F29" s="1" t="inlineStr">
+        <is>
+          <t>closing_price_usd</t>
+        </is>
+      </c>
       <c r="G29" s="1" t="n"/>
       <c r="H29" s="1" t="n"/>
       <c r="I29" s="1" t="n"/>
@@ -1869,8 +1912,8 @@
     </row>
     <row r="30" ht="12.75" customHeight="1" s="85">
       <c r="A30" s="1" t="n"/>
-      <c r="B30" s="1" t="n"/>
-      <c r="C30" s="1" t="n"/>
+      <c r="B30" s="91" t="n"/>
+      <c r="C30" s="91" t="n"/>
       <c r="D30" s="1" t="n"/>
       <c r="E30" s="1" t="n"/>
       <c r="F30" s="1" t="n"/>
@@ -1897,8 +1940,8 @@
     </row>
     <row r="31" ht="12.75" customHeight="1" s="85">
       <c r="A31" s="1" t="n"/>
-      <c r="B31" s="1" t="n"/>
-      <c r="C31" s="1" t="n"/>
+      <c r="B31" s="91" t="n"/>
+      <c r="C31" s="91" t="n"/>
       <c r="D31" s="1" t="n"/>
       <c r="E31" s="1" t="n"/>
       <c r="F31" s="1" t="n"/>
@@ -1925,8 +1968,8 @@
     </row>
     <row r="32" ht="12.75" customHeight="1" s="85">
       <c r="A32" s="1" t="n"/>
-      <c r="B32" s="1" t="n"/>
-      <c r="C32" s="1" t="n"/>
+      <c r="B32" s="91" t="n"/>
+      <c r="C32" s="91" t="n"/>
       <c r="D32" s="1" t="n"/>
       <c r="E32" s="1" t="n"/>
       <c r="F32" s="1" t="n"/>
@@ -1953,8 +1996,8 @@
     </row>
     <row r="33" ht="12.75" customHeight="1" s="85">
       <c r="A33" s="1" t="n"/>
-      <c r="B33" s="1" t="n"/>
-      <c r="C33" s="1" t="n"/>
+      <c r="B33" s="91" t="n"/>
+      <c r="C33" s="91" t="n"/>
       <c r="D33" s="1" t="n"/>
       <c r="E33" s="1" t="n"/>
       <c r="F33" s="1" t="n"/>
@@ -1981,8 +2024,8 @@
     </row>
     <row r="34" ht="12.75" customHeight="1" s="85">
       <c r="A34" s="1" t="n"/>
-      <c r="B34" s="1" t="n"/>
-      <c r="C34" s="1" t="n"/>
+      <c r="B34" s="91" t="n"/>
+      <c r="C34" s="91" t="n"/>
       <c r="D34" s="1" t="n"/>
       <c r="E34" s="1" t="n"/>
       <c r="F34" s="1" t="n"/>
@@ -2009,8 +2052,8 @@
     </row>
     <row r="35" ht="12.75" customHeight="1" s="85">
       <c r="A35" s="1" t="n"/>
-      <c r="B35" s="1" t="n"/>
-      <c r="C35" s="1" t="n"/>
+      <c r="B35" s="91" t="n"/>
+      <c r="C35" s="91" t="n"/>
       <c r="D35" s="1" t="n"/>
       <c r="E35" s="1" t="n"/>
       <c r="F35" s="1" t="n"/>
@@ -2037,8 +2080,8 @@
     </row>
     <row r="36" ht="12.75" customHeight="1" s="85">
       <c r="A36" s="1" t="n"/>
-      <c r="B36" s="1" t="n"/>
-      <c r="C36" s="1" t="n"/>
+      <c r="B36" s="91" t="n"/>
+      <c r="C36" s="91" t="n"/>
       <c r="D36" s="1" t="n"/>
       <c r="E36" s="1" t="n"/>
       <c r="F36" s="1" t="n"/>
@@ -2065,8 +2108,8 @@
     </row>
     <row r="37" ht="12.75" customHeight="1" s="85">
       <c r="A37" s="1" t="n"/>
-      <c r="B37" s="1" t="n"/>
-      <c r="C37" s="1" t="n"/>
+      <c r="B37" s="91" t="n"/>
+      <c r="C37" s="91" t="n"/>
       <c r="D37" s="1" t="n"/>
       <c r="E37" s="1" t="n"/>
       <c r="F37" s="1" t="n"/>
@@ -2093,8 +2136,8 @@
     </row>
     <row r="38" ht="12.75" customHeight="1" s="85">
       <c r="A38" s="1" t="n"/>
-      <c r="B38" s="1" t="n"/>
-      <c r="C38" s="1" t="n"/>
+      <c r="B38" s="91" t="n"/>
+      <c r="C38" s="91" t="n"/>
       <c r="D38" s="1" t="n"/>
       <c r="E38" s="1" t="n"/>
       <c r="F38" s="1" t="n"/>
@@ -2121,8 +2164,8 @@
     </row>
     <row r="39" ht="12.75" customHeight="1" s="85">
       <c r="A39" s="1" t="n"/>
-      <c r="B39" s="1" t="n"/>
-      <c r="C39" s="1" t="n"/>
+      <c r="B39" s="91" t="n"/>
+      <c r="C39" s="91" t="n"/>
       <c r="D39" s="1" t="n"/>
       <c r="E39" s="1" t="n"/>
       <c r="F39" s="1" t="n"/>
@@ -2149,8 +2192,8 @@
     </row>
     <row r="40" ht="12.75" customHeight="1" s="85">
       <c r="A40" s="1" t="n"/>
-      <c r="B40" s="1" t="n"/>
-      <c r="C40" s="1" t="n"/>
+      <c r="B40" s="91" t="n"/>
+      <c r="C40" s="91" t="n"/>
       <c r="D40" s="1" t="n"/>
       <c r="E40" s="1" t="n"/>
       <c r="F40" s="1" t="n"/>
@@ -2177,8 +2220,8 @@
     </row>
     <row r="41" ht="12.75" customHeight="1" s="85">
       <c r="A41" s="1" t="n"/>
-      <c r="B41" s="1" t="n"/>
-      <c r="C41" s="1" t="n"/>
+      <c r="B41" s="91" t="n"/>
+      <c r="C41" s="91" t="n"/>
       <c r="D41" s="1" t="n"/>
       <c r="E41" s="1" t="n"/>
       <c r="F41" s="1" t="n"/>
@@ -2205,8 +2248,8 @@
     </row>
     <row r="42" ht="12.75" customHeight="1" s="85">
       <c r="A42" s="1" t="n"/>
-      <c r="B42" s="1" t="n"/>
-      <c r="C42" s="1" t="n"/>
+      <c r="B42" s="91" t="n"/>
+      <c r="C42" s="91" t="n"/>
       <c r="D42" s="1" t="n"/>
       <c r="E42" s="1" t="n"/>
       <c r="F42" s="1" t="n"/>
@@ -2233,8 +2276,8 @@
     </row>
     <row r="43" ht="12.75" customHeight="1" s="85">
       <c r="A43" s="1" t="n"/>
-      <c r="B43" s="1" t="n"/>
-      <c r="C43" s="1" t="n"/>
+      <c r="B43" s="91" t="n"/>
+      <c r="C43" s="91" t="n"/>
       <c r="D43" s="1" t="n"/>
       <c r="E43" s="1" t="n"/>
       <c r="F43" s="1" t="n"/>
@@ -2261,8 +2304,8 @@
     </row>
     <row r="44" ht="12.75" customHeight="1" s="85">
       <c r="A44" s="1" t="n"/>
-      <c r="B44" s="1" t="n"/>
-      <c r="C44" s="1" t="n"/>
+      <c r="B44" s="91" t="n"/>
+      <c r="C44" s="91" t="n"/>
       <c r="D44" s="1" t="n"/>
       <c r="E44" s="1" t="n"/>
       <c r="F44" s="1" t="n"/>
@@ -2289,8 +2332,8 @@
     </row>
     <row r="45" ht="12.75" customHeight="1" s="85">
       <c r="A45" s="1" t="n"/>
-      <c r="B45" s="1" t="n"/>
-      <c r="C45" s="1" t="n"/>
+      <c r="B45" s="91" t="n"/>
+      <c r="C45" s="91" t="n"/>
       <c r="D45" s="1" t="n"/>
       <c r="E45" s="1" t="n"/>
       <c r="F45" s="1" t="n"/>

--- a/skills/tax/rsu/template_rsu.xlsx
+++ b/skills/tax/rsu/template_rsu.xlsx
@@ -216,7 +216,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -451,6 +451,38 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -779,16 +811,11 @@
           <t>Information declared in prior year (2024)</t>
         </is>
       </c>
-      <c r="C2" s="86" t="n"/>
-      <c r="D2" s="86" t="n"/>
-      <c r="E2" s="86" t="n"/>
-      <c r="F2" s="86" t="n"/>
       <c r="G2" s="87" t="inlineStr">
         <is>
           <t>Detail in the 'Description' field</t>
         </is>
       </c>
-      <c r="H2" s="88" t="n"/>
       <c r="I2" s="6" t="n"/>
       <c r="J2" s="1" t="n"/>
       <c r="K2" s="1" t="n"/>
@@ -936,15 +963,9 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="89" t="inlineStr">
         <is>
-          <t>Vesting of RSUs — totals by release date (auto-computed from the per-grant detail below)</t>
-        </is>
-      </c>
-      <c r="C6" s="86" t="n"/>
-      <c r="D6" s="86" t="n"/>
-      <c r="E6" s="86" t="n"/>
-      <c r="F6" s="86" t="n"/>
-      <c r="G6" s="86" t="n"/>
-      <c r="H6" s="88" t="n"/>
+          <t>Vesting of RSUs — one row per award per release date</t>
+        </is>
+      </c>
       <c r="I6" s="1" t="n"/>
       <c r="J6" s="1" t="n"/>
       <c r="K6" s="1" t="n"/>
@@ -978,31 +999,39 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>quantity_released</t>
+          <t>award_date</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
+          <t>award_number</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>net_quantity</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
           <t>share_closing_price_usd</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>fx_rate_brl_usd_ptax_sell</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="I7" s="1" t="inlineStr">
         <is>
           <t>share_value_brl</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="J7" s="1" t="inlineStr">
         <is>
           <t>total_value_brl</t>
         </is>
       </c>
-      <c r="I7" s="1" t="n"/>
-      <c r="J7" s="1" t="n"/>
       <c r="K7" s="1" t="n"/>
       <c r="L7" s="1" t="n"/>
       <c r="M7" s="1" t="n"/>
@@ -1022,36 +1051,27 @@
     </row>
     <row r="8" ht="12.75" customHeight="1" s="85">
       <c r="A8" s="1" t="n"/>
-      <c r="B8" s="9" t="n">
-        <v>45660</v>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>Vesting</t>
-        </is>
-      </c>
-      <c r="D8" s="11">
-        <f>SUMIFS($E$30:$E$45,$B$30:$B$45,B8)</f>
-        <v/>
-      </c>
-      <c r="E8" s="15">
-        <f>IFERROR(INDEX($F$30:$F$45,MATCH(B8,$B$30:$B$45,0)),0)</f>
-        <v/>
-      </c>
-      <c r="F8" s="17">
-        <f t="array" ref="F8">IFERROR(XLOOKUP(B8,aux_ptax_historical_data!B:B,aux_ptax_historical_data!E:E),"")</f>
-        <v/>
-      </c>
-      <c r="G8" s="18">
-        <f>ROUND(E8*F8,2)</f>
-        <v/>
-      </c>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="10">
+        <f>IF(B8="","","Vesting")</f>
+        <v/>
+      </c>
+      <c r="D8" s="92" t="n"/>
+      <c r="E8" s="15" t="n"/>
+      <c r="F8" s="17" t="n"/>
+      <c r="G8" s="18" t="n"/>
       <c r="H8" s="18">
-        <f>D8*G8</f>
-        <v/>
-      </c>
-      <c r="I8" s="1" t="n"/>
-      <c r="J8" s="1" t="n"/>
+        <f>IFERROR(VLOOKUP(B8,aux_ptax_historical_data!$B:$E,4,0),"")</f>
+        <v/>
+      </c>
+      <c r="I8" s="1">
+        <f>IF(B8="","",ROUND(G8*H8,2))</f>
+        <v/>
+      </c>
+      <c r="J8" s="1">
+        <f>IF(B8="","",F8*I8)</f>
+        <v/>
+      </c>
       <c r="K8" s="1" t="n"/>
       <c r="L8" s="1" t="n"/>
       <c r="M8" s="1" t="n"/>
@@ -1071,36 +1091,27 @@
     </row>
     <row r="9" ht="12.75" customHeight="1" s="85">
       <c r="A9" s="1" t="n"/>
-      <c r="B9" s="9" t="n">
-        <v>45748</v>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>Vesting</t>
-        </is>
-      </c>
-      <c r="D9" s="11">
-        <f>SUMIFS($E$30:$E$45,$B$30:$B$45,B9)</f>
-        <v/>
-      </c>
-      <c r="E9" s="15">
-        <f>IFERROR(INDEX($F$30:$F$45,MATCH(B9,$B$30:$B$45,0)),0)</f>
-        <v/>
-      </c>
-      <c r="F9" s="17">
-        <f t="array" ref="F9">IFERROR(XLOOKUP(B9,aux_ptax_historical_data!B:B,aux_ptax_historical_data!E:E),"")</f>
-        <v/>
-      </c>
-      <c r="G9" s="18">
-        <f>ROUND(E9*F9,2)</f>
-        <v/>
-      </c>
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="10">
+        <f>IF(B9="","","Vesting")</f>
+        <v/>
+      </c>
+      <c r="D9" s="92" t="n"/>
+      <c r="E9" s="15" t="n"/>
+      <c r="F9" s="17" t="n"/>
+      <c r="G9" s="18" t="n"/>
       <c r="H9" s="18">
-        <f>D9*G9</f>
-        <v/>
-      </c>
-      <c r="I9" s="1" t="n"/>
-      <c r="J9" s="1" t="n"/>
+        <f>IFERROR(VLOOKUP(B9,aux_ptax_historical_data!$B:$E,4,0),"")</f>
+        <v/>
+      </c>
+      <c r="I9" s="1">
+        <f>IF(B9="","",ROUND(G9*H9,2))</f>
+        <v/>
+      </c>
+      <c r="J9" s="1">
+        <f>IF(B9="","",F9*I9)</f>
+        <v/>
+      </c>
       <c r="K9" s="1" t="n"/>
       <c r="L9" s="1" t="n"/>
       <c r="M9" s="1" t="n"/>
@@ -1120,36 +1131,27 @@
     </row>
     <row r="10" ht="12.75" customHeight="1" s="85">
       <c r="A10" s="1" t="n"/>
-      <c r="B10" s="9" t="n">
-        <v>45839</v>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>Vesting</t>
-        </is>
-      </c>
-      <c r="D10" s="11">
-        <f>SUMIFS($E$30:$E$45,$B$30:$B$45,B10)</f>
-        <v/>
-      </c>
-      <c r="E10" s="15">
-        <f>IFERROR(INDEX($F$30:$F$45,MATCH(B10,$B$30:$B$45,0)),0)</f>
-        <v/>
-      </c>
-      <c r="F10" s="17">
-        <f t="array" ref="F10">IFERROR(XLOOKUP(B10,aux_ptax_historical_data!B:B,aux_ptax_historical_data!E:E),"")</f>
-        <v/>
-      </c>
-      <c r="G10" s="18">
-        <f>ROUND(E10*F10,2)</f>
-        <v/>
-      </c>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="10">
+        <f>IF(B10="","","Vesting")</f>
+        <v/>
+      </c>
+      <c r="D10" s="92" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="17" t="n"/>
+      <c r="G10" s="18" t="n"/>
       <c r="H10" s="18">
-        <f>D10*G10</f>
-        <v/>
-      </c>
-      <c r="I10" s="1" t="n"/>
-      <c r="J10" s="1" t="n"/>
+        <f>IFERROR(VLOOKUP(B10,aux_ptax_historical_data!$B:$E,4,0),"")</f>
+        <v/>
+      </c>
+      <c r="I10" s="1">
+        <f>IF(B10="","",ROUND(G10*H10,2))</f>
+        <v/>
+      </c>
+      <c r="J10" s="1">
+        <f>IF(B10="","",F10*I10)</f>
+        <v/>
+      </c>
       <c r="K10" s="1" t="n"/>
       <c r="L10" s="1" t="n"/>
       <c r="M10" s="1" t="n"/>
@@ -1169,36 +1171,27 @@
     </row>
     <row r="11" ht="12.75" customHeight="1" s="85">
       <c r="A11" s="1" t="n"/>
-      <c r="B11" s="9" t="n">
-        <v>45931</v>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>Vesting</t>
-        </is>
-      </c>
-      <c r="D11" s="11">
-        <f>SUMIFS($E$30:$E$45,$B$30:$B$45,B11)</f>
-        <v/>
-      </c>
-      <c r="E11" s="15">
-        <f>IFERROR(INDEX($F$30:$F$45,MATCH(B11,$B$30:$B$45,0)),0)</f>
-        <v/>
-      </c>
-      <c r="F11" s="17">
-        <f t="array" ref="F11">IFERROR(XLOOKUP(B11,aux_ptax_historical_data!B:B,aux_ptax_historical_data!E:E),"")</f>
-        <v/>
-      </c>
-      <c r="G11" s="18">
-        <f>ROUND(E11*F11,2)</f>
-        <v/>
-      </c>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="10">
+        <f>IF(B11="","","Vesting")</f>
+        <v/>
+      </c>
+      <c r="D11" s="92" t="n"/>
+      <c r="E11" s="15" t="n"/>
+      <c r="F11" s="17" t="n"/>
+      <c r="G11" s="18" t="n"/>
       <c r="H11" s="18">
-        <f>D11*G11</f>
-        <v/>
-      </c>
-      <c r="I11" s="1" t="n"/>
-      <c r="J11" s="1" t="n"/>
+        <f>IFERROR(VLOOKUP(B11,aux_ptax_historical_data!$B:$E,4,0),"")</f>
+        <v/>
+      </c>
+      <c r="I11" s="1">
+        <f>IF(B11="","",ROUND(G11*H11,2))</f>
+        <v/>
+      </c>
+      <c r="J11" s="1">
+        <f>IF(B11="","",F11*I11)</f>
+        <v/>
+      </c>
       <c r="K11" s="1" t="n"/>
       <c r="L11" s="1" t="n"/>
       <c r="M11" s="1" t="n"/>
@@ -1218,25 +1211,27 @@
     </row>
     <row r="12" ht="12.75" customHeight="1" s="85">
       <c r="A12" s="1" t="n"/>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="C12" s="21" t="n"/>
-      <c r="D12" s="22">
-        <f>SUM(D8:D11)</f>
-        <v/>
-      </c>
+      <c r="B12" s="93" t="n"/>
+      <c r="C12" s="21">
+        <f>IF(B12="","","Vesting")</f>
+        <v/>
+      </c>
+      <c r="D12" s="94" t="n"/>
       <c r="E12" s="21" t="n"/>
       <c r="F12" s="21" t="n"/>
       <c r="G12" s="21" t="n"/>
       <c r="H12" s="23">
-        <f>SUM(H8:H11)</f>
-        <v/>
-      </c>
-      <c r="I12" s="1" t="n"/>
-      <c r="J12" s="1" t="n"/>
+        <f>IFERROR(VLOOKUP(B12,aux_ptax_historical_data!$B:$E,4,0),"")</f>
+        <v/>
+      </c>
+      <c r="I12" s="1">
+        <f>IF(B12="","",ROUND(G12*H12,2))</f>
+        <v/>
+      </c>
+      <c r="J12" s="1">
+        <f>IF(B12="","",F12*I12)</f>
+        <v/>
+      </c>
       <c r="K12" s="1" t="n"/>
       <c r="L12" s="1" t="n"/>
       <c r="M12" s="1" t="n"/>
@@ -1256,15 +1251,27 @@
     </row>
     <row r="13" ht="12.75" customHeight="1" s="85">
       <c r="A13" s="1" t="n"/>
-      <c r="B13" s="1" t="n"/>
-      <c r="C13" s="1" t="n"/>
-      <c r="D13" s="1" t="n"/>
+      <c r="B13" s="91" t="n"/>
+      <c r="C13" s="1">
+        <f>IF(B13="","","Vesting")</f>
+        <v/>
+      </c>
+      <c r="D13" s="91" t="n"/>
       <c r="E13" s="1" t="n"/>
       <c r="F13" s="1" t="n"/>
       <c r="G13" s="1" t="n"/>
-      <c r="H13" s="1" t="n"/>
-      <c r="I13" s="1" t="n"/>
-      <c r="J13" s="1" t="n"/>
+      <c r="H13" s="1">
+        <f>IFERROR(VLOOKUP(B13,aux_ptax_historical_data!$B:$E,4,0),"")</f>
+        <v/>
+      </c>
+      <c r="I13" s="1">
+        <f>IF(B13="","",ROUND(G13*H13,2))</f>
+        <v/>
+      </c>
+      <c r="J13" s="1">
+        <f>IF(B13="","",F13*I13)</f>
+        <v/>
+      </c>
       <c r="K13" s="1" t="n"/>
       <c r="L13" s="1" t="n"/>
       <c r="M13" s="1" t="n"/>
@@ -1284,19 +1291,24 @@
     </row>
     <row r="14" ht="12.75" customHeight="1" s="85">
       <c r="A14" s="1" t="n"/>
-      <c r="B14" s="89" t="inlineStr">
-        <is>
-          <t>Sale of shares (if applicable)</t>
-        </is>
-      </c>
-      <c r="C14" s="86" t="n"/>
-      <c r="D14" s="86" t="n"/>
-      <c r="E14" s="86" t="n"/>
-      <c r="F14" s="86" t="n"/>
-      <c r="G14" s="86" t="n"/>
-      <c r="H14" s="88" t="n"/>
-      <c r="I14" s="1" t="n"/>
-      <c r="J14" s="1" t="n"/>
+      <c r="B14" s="95" t="n"/>
+      <c r="C14">
+        <f>IF(B14="","","Vesting")</f>
+        <v/>
+      </c>
+      <c r="D14" s="96" t="n"/>
+      <c r="H14">
+        <f>IFERROR(VLOOKUP(B14,aux_ptax_historical_data!$B:$E,4,0),"")</f>
+        <v/>
+      </c>
+      <c r="I14" s="1">
+        <f>IF(B14="","",ROUND(G14*H14,2))</f>
+        <v/>
+      </c>
+      <c r="J14" s="1">
+        <f>IF(B14="","",F14*I14)</f>
+        <v/>
+      </c>
       <c r="K14" s="1" t="n"/>
       <c r="L14" s="1" t="n"/>
       <c r="M14" s="1" t="n"/>
@@ -1316,43 +1328,27 @@
     </row>
     <row r="15" ht="12.75" customHeight="1" s="85">
       <c r="A15" s="1" t="n"/>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>event</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>quantity_sold</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>sale_price_usd</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>fx_rate_brl_usd_ptax_buy</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>share_value_brl</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t>total_value_brl</t>
-        </is>
-      </c>
-      <c r="I15" s="24" t="n"/>
-      <c r="J15" s="24" t="n"/>
+      <c r="B15" s="97" t="n"/>
+      <c r="C15" s="7">
+        <f>IF(B15="","","Vesting")</f>
+        <v/>
+      </c>
+      <c r="D15" s="98" t="n"/>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="8" t="n"/>
+      <c r="G15" s="8" t="n"/>
+      <c r="H15" s="8">
+        <f>IFERROR(VLOOKUP(B15,aux_ptax_historical_data!$B:$E,4,0),"")</f>
+        <v/>
+      </c>
+      <c r="I15" s="24">
+        <f>IF(B15="","",ROUND(G15*H15,2))</f>
+        <v/>
+      </c>
+      <c r="J15" s="24">
+        <f>IF(B15="","",F15*I15)</f>
+        <v/>
+      </c>
       <c r="K15" s="24" t="n"/>
       <c r="L15" s="24" t="n"/>
       <c r="M15" s="1" t="n"/>
@@ -1372,27 +1368,27 @@
     </row>
     <row r="16" ht="12.75" customHeight="1" s="85">
       <c r="A16" s="1" t="n"/>
-      <c r="B16" s="25" t="n"/>
+      <c r="B16" s="99" t="n"/>
       <c r="C16" s="26">
-        <f>IF(B16="","","Venda")</f>
-        <v/>
-      </c>
-      <c r="D16" s="27" t="n"/>
+        <f>IF(B16="","","Vesting")</f>
+        <v/>
+      </c>
+      <c r="D16" s="100" t="n"/>
       <c r="E16" s="28" t="n"/>
-      <c r="F16" s="29">
-        <f t="array" ref="F16">IFERROR(XLOOKUP(B16,aux_ptax_historical_data!B:B,aux_ptax_historical_data!D:D),"")</f>
-        <v/>
-      </c>
-      <c r="G16" s="30">
-        <f>IF(B16="","",ROUND(E16*F16,2))</f>
-        <v/>
-      </c>
+      <c r="F16" s="29" t="n"/>
+      <c r="G16" s="30" t="n"/>
       <c r="H16" s="30">
-        <f>IF(B16="","",D16*G16)</f>
-        <v/>
-      </c>
-      <c r="I16" s="31" t="n"/>
-      <c r="J16" s="32" t="n"/>
+        <f>IFERROR(VLOOKUP(B16,aux_ptax_historical_data!$B:$E,4,0),"")</f>
+        <v/>
+      </c>
+      <c r="I16" s="31">
+        <f>IF(B16="","",ROUND(G16*H16,2))</f>
+        <v/>
+      </c>
+      <c r="J16" s="32">
+        <f>IF(B16="","",F16*I16)</f>
+        <v/>
+      </c>
       <c r="K16" s="32" t="n"/>
       <c r="L16" s="31" t="n"/>
       <c r="M16" s="1" t="n"/>
@@ -1412,27 +1408,27 @@
     </row>
     <row r="17" ht="12.75" customHeight="1" s="85">
       <c r="A17" s="1" t="n"/>
-      <c r="B17" s="25" t="n"/>
+      <c r="B17" s="99" t="n"/>
       <c r="C17" s="26">
-        <f>IF(B17="","","Venda")</f>
-        <v/>
-      </c>
-      <c r="D17" s="27" t="n"/>
+        <f>IF(B17="","","Vesting")</f>
+        <v/>
+      </c>
+      <c r="D17" s="100" t="n"/>
       <c r="E17" s="28" t="n"/>
-      <c r="F17" s="29">
-        <f t="array" ref="F17">IFERROR(XLOOKUP(B17,aux_ptax_historical_data!B:B,aux_ptax_historical_data!D:D),"")</f>
-        <v/>
-      </c>
-      <c r="G17" s="30">
-        <f>IF(B17="","",ROUND(E17*F17,2))</f>
-        <v/>
-      </c>
+      <c r="F17" s="29" t="n"/>
+      <c r="G17" s="30" t="n"/>
       <c r="H17" s="30">
-        <f>IF(B17="","",D17*G17)</f>
-        <v/>
-      </c>
-      <c r="I17" s="31" t="n"/>
-      <c r="J17" s="32" t="n"/>
+        <f>IFERROR(VLOOKUP(B17,aux_ptax_historical_data!$B:$E,4,0),"")</f>
+        <v/>
+      </c>
+      <c r="I17" s="31">
+        <f>IF(B17="","",ROUND(G17*H17,2))</f>
+        <v/>
+      </c>
+      <c r="J17" s="32">
+        <f>IF(B17="","",F17*I17)</f>
+        <v/>
+      </c>
       <c r="K17" s="32" t="n"/>
       <c r="L17" s="31" t="n"/>
       <c r="M17" s="1" t="n"/>
@@ -1452,27 +1448,27 @@
     </row>
     <row r="18" ht="12.75" customHeight="1" s="85">
       <c r="A18" s="1" t="n"/>
-      <c r="B18" s="25" t="n"/>
+      <c r="B18" s="99" t="n"/>
       <c r="C18" s="26">
-        <f>IF(B18="","","Venda")</f>
-        <v/>
-      </c>
-      <c r="D18" s="27" t="n"/>
+        <f>IF(B18="","","Vesting")</f>
+        <v/>
+      </c>
+      <c r="D18" s="100" t="n"/>
       <c r="E18" s="28" t="n"/>
-      <c r="F18" s="29">
-        <f t="array" ref="F18">IFERROR(XLOOKUP(B18,aux_ptax_historical_data!B:B,aux_ptax_historical_data!D:D),"")</f>
-        <v/>
-      </c>
-      <c r="G18" s="30">
-        <f>IF(B18="","",ROUND(E18*F18,2))</f>
-        <v/>
-      </c>
+      <c r="F18" s="29" t="n"/>
+      <c r="G18" s="30" t="n"/>
       <c r="H18" s="30">
-        <f>IF(B18="","",D18*G18)</f>
-        <v/>
-      </c>
-      <c r="I18" s="31" t="n"/>
-      <c r="J18" s="32" t="n"/>
+        <f>IFERROR(VLOOKUP(B18,aux_ptax_historical_data!$B:$E,4,0),"")</f>
+        <v/>
+      </c>
+      <c r="I18" s="31">
+        <f>IF(B18="","",ROUND(G18*H18,2))</f>
+        <v/>
+      </c>
+      <c r="J18" s="32">
+        <f>IF(B18="","",F18*I18)</f>
+        <v/>
+      </c>
       <c r="K18" s="32" t="n"/>
       <c r="L18" s="31" t="n"/>
       <c r="M18" s="1" t="n"/>
@@ -1492,27 +1488,27 @@
     </row>
     <row r="19" ht="12.75" customHeight="1" s="85">
       <c r="A19" s="1" t="n"/>
-      <c r="B19" s="25" t="n"/>
+      <c r="B19" s="99" t="n"/>
       <c r="C19" s="26">
-        <f>IF(B19="","","Venda")</f>
-        <v/>
-      </c>
-      <c r="D19" s="27" t="n"/>
+        <f>IF(B19="","","Vesting")</f>
+        <v/>
+      </c>
+      <c r="D19" s="100" t="n"/>
       <c r="E19" s="28" t="n"/>
-      <c r="F19" s="29">
-        <f t="array" ref="F19">IFERROR(XLOOKUP(B19,aux_ptax_historical_data!B:B,aux_ptax_historical_data!D:D),"")</f>
-        <v/>
-      </c>
-      <c r="G19" s="30">
-        <f>IF(B19="","",ROUND(E19*F19,2))</f>
-        <v/>
-      </c>
+      <c r="F19" s="29" t="n"/>
+      <c r="G19" s="30" t="n"/>
       <c r="H19" s="30">
-        <f>IF(B19="","",D19*G19)</f>
-        <v/>
-      </c>
-      <c r="I19" s="31" t="n"/>
-      <c r="J19" s="32" t="n"/>
+        <f>IFERROR(VLOOKUP(B19,aux_ptax_historical_data!$B:$E,4,0),"")</f>
+        <v/>
+      </c>
+      <c r="I19" s="31">
+        <f>IF(B19="","",ROUND(G19*H19,2))</f>
+        <v/>
+      </c>
+      <c r="J19" s="32">
+        <f>IF(B19="","",F19*I19)</f>
+        <v/>
+      </c>
       <c r="K19" s="32" t="n"/>
       <c r="L19" s="31" t="n"/>
       <c r="M19" s="1" t="n"/>
@@ -1532,27 +1528,27 @@
     </row>
     <row r="20" ht="12.75" customHeight="1" s="85">
       <c r="A20" s="1" t="n"/>
-      <c r="B20" s="25" t="n"/>
+      <c r="B20" s="99" t="n"/>
       <c r="C20" s="26">
-        <f>IF(B20="","","Venda")</f>
-        <v/>
-      </c>
-      <c r="D20" s="27" t="n"/>
+        <f>IF(B20="","","Vesting")</f>
+        <v/>
+      </c>
+      <c r="D20" s="100" t="n"/>
       <c r="E20" s="28" t="n"/>
-      <c r="F20" s="29">
-        <f t="array" ref="F20">IFERROR(XLOOKUP(B20,aux_ptax_historical_data!B:B,aux_ptax_historical_data!D:D),"")</f>
-        <v/>
-      </c>
-      <c r="G20" s="30">
-        <f>IF(B20="","",ROUND(E20*F20,2))</f>
-        <v/>
-      </c>
+      <c r="F20" s="29" t="n"/>
+      <c r="G20" s="30" t="n"/>
       <c r="H20" s="30">
-        <f>IF(B20="","",D20*G20)</f>
-        <v/>
-      </c>
-      <c r="I20" s="31" t="n"/>
-      <c r="J20" s="32" t="n"/>
+        <f>IFERROR(VLOOKUP(B20,aux_ptax_historical_data!$B:$E,4,0),"")</f>
+        <v/>
+      </c>
+      <c r="I20" s="31">
+        <f>IF(B20="","",ROUND(G20*H20,2))</f>
+        <v/>
+      </c>
+      <c r="J20" s="32">
+        <f>IF(B20="","",F20*I20)</f>
+        <v/>
+      </c>
       <c r="K20" s="32" t="n"/>
       <c r="L20" s="31" t="n"/>
       <c r="M20" s="1" t="n"/>
@@ -1572,24 +1568,27 @@
     </row>
     <row r="21" ht="12.75" customHeight="1" s="85">
       <c r="A21" s="1" t="n"/>
-      <c r="B21" s="33" t="n"/>
-      <c r="C21" s="26" t="n"/>
-      <c r="D21" s="34" t="n"/>
+      <c r="B21" s="101" t="n"/>
+      <c r="C21" s="26">
+        <f>IF(B21="","","Vesting")</f>
+        <v/>
+      </c>
+      <c r="D21" s="102" t="n"/>
       <c r="E21" s="35" t="n"/>
-      <c r="F21" s="29">
-        <f t="array" ref="F21">IFERROR(XLOOKUP(B21,aux_ptax_historical_data!B:B,aux_ptax_historical_data!D:D),"")</f>
-        <v/>
-      </c>
-      <c r="G21" s="30">
-        <f>IF(B21="","",ROUND(E21*F21,2))</f>
-        <v/>
-      </c>
+      <c r="F21" s="29" t="n"/>
+      <c r="G21" s="30" t="n"/>
       <c r="H21" s="30">
-        <f>IF(B21="","",D21*G21)</f>
-        <v/>
-      </c>
-      <c r="I21" s="31" t="n"/>
-      <c r="J21" s="32" t="n"/>
+        <f>IFERROR(VLOOKUP(B21,aux_ptax_historical_data!$B:$E,4,0),"")</f>
+        <v/>
+      </c>
+      <c r="I21" s="31">
+        <f>IF(B21="","",ROUND(G21*H21,2))</f>
+        <v/>
+      </c>
+      <c r="J21" s="32">
+        <f>IF(B21="","",F21*I21)</f>
+        <v/>
+      </c>
       <c r="K21" s="32" t="n"/>
       <c r="L21" s="31" t="n"/>
       <c r="M21" s="1" t="n"/>
@@ -1609,24 +1608,27 @@
     </row>
     <row r="22" ht="12.75" customHeight="1" s="85">
       <c r="A22" s="1" t="n"/>
-      <c r="B22" s="33" t="n"/>
-      <c r="C22" s="26" t="n"/>
-      <c r="D22" s="34" t="n"/>
+      <c r="B22" s="101" t="n"/>
+      <c r="C22" s="26">
+        <f>IF(B22="","","Vesting")</f>
+        <v/>
+      </c>
+      <c r="D22" s="102" t="n"/>
       <c r="E22" s="35" t="n"/>
-      <c r="F22" s="29">
-        <f t="array" ref="F22">IFERROR(XLOOKUP(B22,aux_ptax_historical_data!B:B,aux_ptax_historical_data!D:D),"")</f>
-        <v/>
-      </c>
-      <c r="G22" s="30">
-        <f>IF(B22="","",ROUND(E22*F22,2))</f>
-        <v/>
-      </c>
+      <c r="F22" s="29" t="n"/>
+      <c r="G22" s="30" t="n"/>
       <c r="H22" s="30">
-        <f>IF(B22="","",D22*G22)</f>
-        <v/>
-      </c>
-      <c r="I22" s="31" t="n"/>
-      <c r="J22" s="32" t="n"/>
+        <f>IFERROR(VLOOKUP(B22,aux_ptax_historical_data!$B:$E,4,0),"")</f>
+        <v/>
+      </c>
+      <c r="I22" s="31">
+        <f>IF(B22="","",ROUND(G22*H22,2))</f>
+        <v/>
+      </c>
+      <c r="J22" s="32">
+        <f>IF(B22="","",F22*I22)</f>
+        <v/>
+      </c>
       <c r="K22" s="32" t="n"/>
       <c r="L22" s="31" t="n"/>
       <c r="M22" s="1" t="n"/>
@@ -1646,27 +1648,27 @@
     </row>
     <row r="23" ht="12.75" customHeight="1" s="85">
       <c r="A23" s="1" t="n"/>
-      <c r="B23" s="33" t="n"/>
+      <c r="B23" s="101" t="n"/>
       <c r="C23" s="26">
-        <f>IF(B23="","","Venda")</f>
-        <v/>
-      </c>
-      <c r="D23" s="34" t="n"/>
+        <f>IF(B23="","","Vesting")</f>
+        <v/>
+      </c>
+      <c r="D23" s="102" t="n"/>
       <c r="E23" s="36" t="n"/>
-      <c r="F23" s="29">
-        <f t="array" ref="F23">IFERROR(XLOOKUP(B23,aux_ptax_historical_data!B:B,aux_ptax_historical_data!D:D),"")</f>
-        <v/>
-      </c>
-      <c r="G23" s="30">
-        <f>IF(B23="","",ROUND(E23*F23,2))</f>
-        <v/>
-      </c>
+      <c r="F23" s="29" t="n"/>
+      <c r="G23" s="30" t="n"/>
       <c r="H23" s="30">
-        <f>IF(B23="","",D23*G23)</f>
-        <v/>
-      </c>
-      <c r="I23" s="37" t="n"/>
-      <c r="J23" s="1" t="n"/>
+        <f>IFERROR(VLOOKUP(B23,aux_ptax_historical_data!$B:$E,4,0),"")</f>
+        <v/>
+      </c>
+      <c r="I23" s="37">
+        <f>IF(B23="","",ROUND(G23*H23,2))</f>
+        <v/>
+      </c>
+      <c r="J23" s="1">
+        <f>IF(B23="","",F23*I23)</f>
+        <v/>
+      </c>
       <c r="K23" s="1" t="n"/>
       <c r="L23" s="1" t="n"/>
       <c r="M23" s="1" t="n"/>
@@ -1686,27 +1688,27 @@
     </row>
     <row r="24" ht="12.75" customHeight="1" s="85">
       <c r="A24" s="1" t="n"/>
-      <c r="B24" s="33" t="n"/>
+      <c r="B24" s="101" t="n"/>
       <c r="C24" s="26">
-        <f>IF(B24="","","Venda")</f>
-        <v/>
-      </c>
-      <c r="D24" s="34" t="n"/>
+        <f>IF(B24="","","Vesting")</f>
+        <v/>
+      </c>
+      <c r="D24" s="102" t="n"/>
       <c r="E24" s="36" t="n"/>
-      <c r="F24" s="29">
-        <f t="array" ref="F24">IFERROR(XLOOKUP(B24,aux_ptax_historical_data!B:B,aux_ptax_historical_data!D:D),"")</f>
-        <v/>
-      </c>
-      <c r="G24" s="30">
-        <f>IF(B24="","",ROUND(E24*F24,2))</f>
-        <v/>
-      </c>
+      <c r="F24" s="29" t="n"/>
+      <c r="G24" s="30" t="n"/>
       <c r="H24" s="30">
-        <f>IF(B24="","",D24*G24)</f>
-        <v/>
-      </c>
-      <c r="I24" s="37" t="n"/>
-      <c r="J24" s="1" t="n"/>
+        <f>IFERROR(VLOOKUP(B24,aux_ptax_historical_data!$B:$E,4,0),"")</f>
+        <v/>
+      </c>
+      <c r="I24" s="37">
+        <f>IF(B24="","",ROUND(G24*H24,2))</f>
+        <v/>
+      </c>
+      <c r="J24" s="1">
+        <f>IF(B24="","",F24*I24)</f>
+        <v/>
+      </c>
       <c r="K24" s="1" t="n"/>
       <c r="L24" s="1" t="n"/>
       <c r="M24" s="1" t="n"/>
@@ -1726,27 +1728,27 @@
     </row>
     <row r="25" ht="12.75" customHeight="1" s="85">
       <c r="A25" s="1" t="n"/>
-      <c r="B25" s="33" t="n"/>
+      <c r="B25" s="101" t="n"/>
       <c r="C25" s="26">
-        <f>IF(B25="","","Venda")</f>
-        <v/>
-      </c>
-      <c r="D25" s="34" t="n"/>
+        <f>IF(B25="","","Vesting")</f>
+        <v/>
+      </c>
+      <c r="D25" s="102" t="n"/>
       <c r="E25" s="36" t="n"/>
-      <c r="F25" s="29">
-        <f t="array" ref="F25">IFERROR(XLOOKUP(B25,aux_ptax_historical_data!B:B,aux_ptax_historical_data!D:D),"")</f>
-        <v/>
-      </c>
-      <c r="G25" s="30">
-        <f>IF(B25="","",ROUND(E25*F25,2))</f>
-        <v/>
-      </c>
+      <c r="F25" s="29" t="n"/>
+      <c r="G25" s="30" t="n"/>
       <c r="H25" s="30">
-        <f>IF(B25="","",D25*G25)</f>
-        <v/>
-      </c>
-      <c r="I25" s="37" t="n"/>
-      <c r="J25" s="1" t="n"/>
+        <f>IFERROR(VLOOKUP(B25,aux_ptax_historical_data!$B:$E,4,0),"")</f>
+        <v/>
+      </c>
+      <c r="I25" s="37">
+        <f>IF(B25="","",ROUND(G25*H25,2))</f>
+        <v/>
+      </c>
+      <c r="J25" s="1">
+        <f>IF(B25="","",F25*I25)</f>
+        <v/>
+      </c>
       <c r="K25" s="1" t="n"/>
       <c r="L25" s="1" t="n"/>
       <c r="M25" s="1" t="n"/>
@@ -1766,25 +1768,27 @@
     </row>
     <row r="26" ht="12.75" customHeight="1" s="85">
       <c r="A26" s="1" t="n"/>
-      <c r="B26" s="38" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="C26" s="38" t="n"/>
-      <c r="D26" s="39">
-        <f>SUM(D16:D25)</f>
-        <v/>
-      </c>
+      <c r="B26" s="103" t="n"/>
+      <c r="C26" s="38">
+        <f>IF(B26="","","Vesting")</f>
+        <v/>
+      </c>
+      <c r="D26" s="103" t="n"/>
       <c r="E26" s="38" t="n"/>
       <c r="F26" s="38" t="n"/>
       <c r="G26" s="38" t="n"/>
       <c r="H26" s="40">
-        <f>SUM(H16:H25)</f>
-        <v/>
-      </c>
-      <c r="I26" s="37" t="n"/>
-      <c r="J26" s="1" t="n"/>
+        <f>IFERROR(VLOOKUP(B26,aux_ptax_historical_data!$B:$E,4,0),"")</f>
+        <v/>
+      </c>
+      <c r="I26" s="37">
+        <f>IF(B26="","",ROUND(G26*H26,2))</f>
+        <v/>
+      </c>
+      <c r="J26" s="1">
+        <f>IF(B26="","",F26*I26)</f>
+        <v/>
+      </c>
       <c r="K26" s="1" t="n"/>
       <c r="L26" s="1" t="n"/>
       <c r="M26" s="1" t="n"/>
@@ -1804,15 +1808,27 @@
     </row>
     <row r="27" ht="12.75" customHeight="1" s="85">
       <c r="A27" s="1" t="n"/>
-      <c r="B27" s="1" t="n"/>
-      <c r="C27" s="1" t="n"/>
-      <c r="D27" s="1" t="n"/>
+      <c r="B27" s="91" t="n"/>
+      <c r="C27" s="1">
+        <f>IF(B27="","","Vesting")</f>
+        <v/>
+      </c>
+      <c r="D27" s="91" t="n"/>
       <c r="E27" s="1" t="n"/>
       <c r="F27" s="1" t="n"/>
       <c r="G27" s="1" t="n"/>
-      <c r="H27" s="41" t="n"/>
-      <c r="I27" s="41" t="n"/>
-      <c r="J27" s="1" t="n"/>
+      <c r="H27" s="41">
+        <f>IFERROR(VLOOKUP(B27,aux_ptax_historical_data!$B:$E,4,0),"")</f>
+        <v/>
+      </c>
+      <c r="I27" s="41">
+        <f>IF(B27="","",ROUND(G27*H27,2))</f>
+        <v/>
+      </c>
+      <c r="J27" s="1">
+        <f>IF(B27="","",F27*I27)</f>
+        <v/>
+      </c>
       <c r="K27" s="1" t="n"/>
       <c r="L27" s="1" t="n"/>
       <c r="M27" s="1" t="n"/>
@@ -1832,19 +1848,27 @@
     </row>
     <row r="28" ht="12.75" customHeight="1" s="85">
       <c r="A28" s="1" t="n"/>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>Vesting detail — enter one row per grant (release_date, award_date, award_number, net quantity, closing price)</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="n"/>
-      <c r="D28" s="1" t="n"/>
+      <c r="B28" s="91" t="n"/>
+      <c r="C28" s="1">
+        <f>IF(B28="","","Vesting")</f>
+        <v/>
+      </c>
+      <c r="D28" s="91" t="n"/>
       <c r="E28" s="1" t="n"/>
       <c r="F28" s="1" t="n"/>
       <c r="G28" s="1" t="n"/>
-      <c r="H28" s="1" t="n"/>
-      <c r="I28" s="1" t="n"/>
-      <c r="J28" s="1" t="n"/>
+      <c r="H28" s="1">
+        <f>IFERROR(VLOOKUP(B28,aux_ptax_historical_data!$B:$E,4,0),"")</f>
+        <v/>
+      </c>
+      <c r="I28" s="1">
+        <f>IF(B28="","",ROUND(G28*H28,2))</f>
+        <v/>
+      </c>
+      <c r="J28" s="1">
+        <f>IF(B28="","",F28*I28)</f>
+        <v/>
+      </c>
       <c r="K28" s="1" t="n"/>
       <c r="L28" s="1" t="n"/>
       <c r="M28" s="1" t="n"/>
@@ -1864,35 +1888,27 @@
     </row>
     <row r="29" ht="12.75" customHeight="1" s="85">
       <c r="A29" s="1" t="n"/>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>release_date</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>award_date</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>award_number</t>
-        </is>
-      </c>
-      <c r="E29" s="1" t="inlineStr">
-        <is>
-          <t>net_quantity</t>
-        </is>
-      </c>
-      <c r="F29" s="1" t="inlineStr">
-        <is>
-          <t>closing_price_usd</t>
-        </is>
-      </c>
+      <c r="B29" s="91" t="n"/>
+      <c r="C29" s="1">
+        <f>IF(B29="","","Vesting")</f>
+        <v/>
+      </c>
+      <c r="D29" s="91" t="n"/>
+      <c r="E29" s="1" t="n"/>
+      <c r="F29" s="1" t="n"/>
       <c r="G29" s="1" t="n"/>
-      <c r="H29" s="1" t="n"/>
-      <c r="I29" s="1" t="n"/>
-      <c r="J29" s="1" t="n"/>
+      <c r="H29" s="1">
+        <f>IFERROR(VLOOKUP(B29,aux_ptax_historical_data!$B:$E,4,0),"")</f>
+        <v/>
+      </c>
+      <c r="I29" s="1">
+        <f>IF(B29="","",ROUND(G29*H29,2))</f>
+        <v/>
+      </c>
+      <c r="J29" s="1">
+        <f>IF(B29="","",F29*I29)</f>
+        <v/>
+      </c>
       <c r="K29" s="1" t="n"/>
       <c r="L29" s="1" t="n"/>
       <c r="M29" s="1" t="n"/>
@@ -1913,14 +1929,26 @@
     <row r="30" ht="12.75" customHeight="1" s="85">
       <c r="A30" s="1" t="n"/>
       <c r="B30" s="91" t="n"/>
-      <c r="C30" s="91" t="n"/>
-      <c r="D30" s="1" t="n"/>
+      <c r="C30" s="91">
+        <f>IF(B30="","","Vesting")</f>
+        <v/>
+      </c>
+      <c r="D30" s="91" t="n"/>
       <c r="E30" s="1" t="n"/>
       <c r="F30" s="1" t="n"/>
       <c r="G30" s="1" t="n"/>
-      <c r="H30" s="1" t="n"/>
-      <c r="I30" s="1" t="n"/>
-      <c r="J30" s="1" t="n"/>
+      <c r="H30" s="1">
+        <f>IFERROR(VLOOKUP(B30,aux_ptax_historical_data!$B:$E,4,0),"")</f>
+        <v/>
+      </c>
+      <c r="I30" s="1">
+        <f>IF(B30="","",ROUND(G30*H30,2))</f>
+        <v/>
+      </c>
+      <c r="J30" s="1">
+        <f>IF(B30="","",F30*I30)</f>
+        <v/>
+      </c>
       <c r="K30" s="1" t="n"/>
       <c r="L30" s="1" t="n"/>
       <c r="M30" s="1" t="n"/>
@@ -1941,14 +1969,26 @@
     <row r="31" ht="12.75" customHeight="1" s="85">
       <c r="A31" s="1" t="n"/>
       <c r="B31" s="91" t="n"/>
-      <c r="C31" s="91" t="n"/>
-      <c r="D31" s="1" t="n"/>
+      <c r="C31" s="91">
+        <f>IF(B31="","","Vesting")</f>
+        <v/>
+      </c>
+      <c r="D31" s="91" t="n"/>
       <c r="E31" s="1" t="n"/>
       <c r="F31" s="1" t="n"/>
       <c r="G31" s="1" t="n"/>
-      <c r="H31" s="1" t="n"/>
-      <c r="I31" s="1" t="n"/>
-      <c r="J31" s="1" t="n"/>
+      <c r="H31" s="1">
+        <f>IFERROR(VLOOKUP(B31,aux_ptax_historical_data!$B:$E,4,0),"")</f>
+        <v/>
+      </c>
+      <c r="I31" s="1">
+        <f>IF(B31="","",ROUND(G31*H31,2))</f>
+        <v/>
+      </c>
+      <c r="J31" s="1">
+        <f>IF(B31="","",F31*I31)</f>
+        <v/>
+      </c>
       <c r="K31" s="1" t="n"/>
       <c r="L31" s="1" t="n"/>
       <c r="M31" s="1" t="n"/>
@@ -1996,15 +2036,25 @@
     </row>
     <row r="33" ht="12.75" customHeight="1" s="85">
       <c r="A33" s="1" t="n"/>
-      <c r="B33" s="91" t="n"/>
+      <c r="B33" s="91" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
       <c r="C33" s="91" t="n"/>
       <c r="D33" s="1" t="n"/>
       <c r="E33" s="1" t="n"/>
-      <c r="F33" s="1" t="n"/>
+      <c r="F33" s="1">
+        <f>SUM(F8:F31)</f>
+        <v/>
+      </c>
       <c r="G33" s="1" t="n"/>
       <c r="H33" s="1" t="n"/>
       <c r="I33" s="1" t="n"/>
-      <c r="J33" s="1" t="n"/>
+      <c r="J33" s="1">
+        <f>SUM(J8:J31)</f>
+        <v/>
+      </c>
       <c r="K33" s="1" t="n"/>
       <c r="L33" s="1" t="n"/>
       <c r="M33" s="1" t="n"/>
@@ -2052,7 +2102,11 @@
     </row>
     <row r="35" ht="12.75" customHeight="1" s="85">
       <c r="A35" s="1" t="n"/>
-      <c r="B35" s="91" t="n"/>
+      <c r="B35" s="91" t="inlineStr">
+        <is>
+          <t>Sale of shares (if applicable)</t>
+        </is>
+      </c>
       <c r="C35" s="91" t="n"/>
       <c r="D35" s="1" t="n"/>
       <c r="E35" s="1" t="n"/>
@@ -2080,13 +2134,41 @@
     </row>
     <row r="36" ht="12.75" customHeight="1" s="85">
       <c r="A36" s="1" t="n"/>
-      <c r="B36" s="91" t="n"/>
-      <c r="C36" s="91" t="n"/>
-      <c r="D36" s="1" t="n"/>
-      <c r="E36" s="1" t="n"/>
-      <c r="F36" s="1" t="n"/>
-      <c r="G36" s="1" t="n"/>
-      <c r="H36" s="1" t="n"/>
+      <c r="B36" s="91" t="inlineStr">
+        <is>
+          <t>sale_date</t>
+        </is>
+      </c>
+      <c r="C36" s="91" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="inlineStr">
+        <is>
+          <t>quantity_sold</t>
+        </is>
+      </c>
+      <c r="E36" s="1" t="inlineStr">
+        <is>
+          <t>sale_price_usd</t>
+        </is>
+      </c>
+      <c r="F36" s="1" t="inlineStr">
+        <is>
+          <t>fx_rate_brl_usd_ptax_buy</t>
+        </is>
+      </c>
+      <c r="G36" s="1" t="inlineStr">
+        <is>
+          <t>share_value_brl</t>
+        </is>
+      </c>
+      <c r="H36" s="1" t="inlineStr">
+        <is>
+          <t>total_value_brl</t>
+        </is>
+      </c>
       <c r="I36" s="1" t="n"/>
       <c r="J36" s="1" t="n"/>
       <c r="K36" s="1" t="n"/>
@@ -2109,12 +2191,24 @@
     <row r="37" ht="12.75" customHeight="1" s="85">
       <c r="A37" s="1" t="n"/>
       <c r="B37" s="91" t="n"/>
-      <c r="C37" s="91" t="n"/>
+      <c r="C37" s="91">
+        <f>IF(B37="","","Sale")</f>
+        <v/>
+      </c>
       <c r="D37" s="1" t="n"/>
       <c r="E37" s="1" t="n"/>
-      <c r="F37" s="1" t="n"/>
-      <c r="G37" s="1" t="n"/>
-      <c r="H37" s="1" t="n"/>
+      <c r="F37" s="1">
+        <f>IFERROR(VLOOKUP(B37,aux_ptax_historical_data!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="1">
+        <f>IF(B37="","",ROUND(E37*F37,2))</f>
+        <v/>
+      </c>
+      <c r="H37" s="1">
+        <f>IF(B37="","",D37*G37)</f>
+        <v/>
+      </c>
       <c r="I37" s="1" t="n"/>
       <c r="J37" s="1" t="n"/>
       <c r="K37" s="1" t="n"/>
@@ -2137,12 +2231,24 @@
     <row r="38" ht="12.75" customHeight="1" s="85">
       <c r="A38" s="1" t="n"/>
       <c r="B38" s="91" t="n"/>
-      <c r="C38" s="91" t="n"/>
+      <c r="C38" s="91">
+        <f>IF(B38="","","Sale")</f>
+        <v/>
+      </c>
       <c r="D38" s="1" t="n"/>
       <c r="E38" s="1" t="n"/>
-      <c r="F38" s="1" t="n"/>
-      <c r="G38" s="1" t="n"/>
-      <c r="H38" s="1" t="n"/>
+      <c r="F38" s="1">
+        <f>IFERROR(VLOOKUP(B38,aux_ptax_historical_data!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="G38" s="1">
+        <f>IF(B38="","",ROUND(E38*F38,2))</f>
+        <v/>
+      </c>
+      <c r="H38" s="1">
+        <f>IF(B38="","",D38*G38)</f>
+        <v/>
+      </c>
       <c r="I38" s="1" t="n"/>
       <c r="J38" s="1" t="n"/>
       <c r="K38" s="1" t="n"/>
@@ -2165,12 +2271,24 @@
     <row r="39" ht="12.75" customHeight="1" s="85">
       <c r="A39" s="1" t="n"/>
       <c r="B39" s="91" t="n"/>
-      <c r="C39" s="91" t="n"/>
+      <c r="C39" s="91">
+        <f>IF(B39="","","Sale")</f>
+        <v/>
+      </c>
       <c r="D39" s="1" t="n"/>
       <c r="E39" s="1" t="n"/>
-      <c r="F39" s="1" t="n"/>
-      <c r="G39" s="1" t="n"/>
-      <c r="H39" s="1" t="n"/>
+      <c r="F39" s="1">
+        <f>IFERROR(VLOOKUP(B39,aux_ptax_historical_data!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="G39" s="1">
+        <f>IF(B39="","",ROUND(E39*F39,2))</f>
+        <v/>
+      </c>
+      <c r="H39" s="1">
+        <f>IF(B39="","",D39*G39)</f>
+        <v/>
+      </c>
       <c r="I39" s="1" t="n"/>
       <c r="J39" s="1" t="n"/>
       <c r="K39" s="1" t="n"/>
@@ -2193,12 +2311,24 @@
     <row r="40" ht="12.75" customHeight="1" s="85">
       <c r="A40" s="1" t="n"/>
       <c r="B40" s="91" t="n"/>
-      <c r="C40" s="91" t="n"/>
+      <c r="C40" s="91">
+        <f>IF(B40="","","Sale")</f>
+        <v/>
+      </c>
       <c r="D40" s="1" t="n"/>
       <c r="E40" s="1" t="n"/>
-      <c r="F40" s="1" t="n"/>
-      <c r="G40" s="1" t="n"/>
-      <c r="H40" s="1" t="n"/>
+      <c r="F40" s="1">
+        <f>IFERROR(VLOOKUP(B40,aux_ptax_historical_data!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="G40" s="1">
+        <f>IF(B40="","",ROUND(E40*F40,2))</f>
+        <v/>
+      </c>
+      <c r="H40" s="1">
+        <f>IF(B40="","",D40*G40)</f>
+        <v/>
+      </c>
       <c r="I40" s="1" t="n"/>
       <c r="J40" s="1" t="n"/>
       <c r="K40" s="1" t="n"/>
@@ -2221,12 +2351,24 @@
     <row r="41" ht="12.75" customHeight="1" s="85">
       <c r="A41" s="1" t="n"/>
       <c r="B41" s="91" t="n"/>
-      <c r="C41" s="91" t="n"/>
+      <c r="C41" s="91">
+        <f>IF(B41="","","Sale")</f>
+        <v/>
+      </c>
       <c r="D41" s="1" t="n"/>
       <c r="E41" s="1" t="n"/>
-      <c r="F41" s="1" t="n"/>
-      <c r="G41" s="1" t="n"/>
-      <c r="H41" s="1" t="n"/>
+      <c r="F41" s="1">
+        <f>IFERROR(VLOOKUP(B41,aux_ptax_historical_data!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="G41" s="1">
+        <f>IF(B41="","",ROUND(E41*F41,2))</f>
+        <v/>
+      </c>
+      <c r="H41" s="1">
+        <f>IF(B41="","",D41*G41)</f>
+        <v/>
+      </c>
       <c r="I41" s="1" t="n"/>
       <c r="J41" s="1" t="n"/>
       <c r="K41" s="1" t="n"/>
@@ -2249,12 +2391,24 @@
     <row r="42" ht="12.75" customHeight="1" s="85">
       <c r="A42" s="1" t="n"/>
       <c r="B42" s="91" t="n"/>
-      <c r="C42" s="91" t="n"/>
+      <c r="C42" s="91">
+        <f>IF(B42="","","Sale")</f>
+        <v/>
+      </c>
       <c r="D42" s="1" t="n"/>
       <c r="E42" s="1" t="n"/>
-      <c r="F42" s="1" t="n"/>
-      <c r="G42" s="1" t="n"/>
-      <c r="H42" s="1" t="n"/>
+      <c r="F42" s="1">
+        <f>IFERROR(VLOOKUP(B42,aux_ptax_historical_data!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="G42" s="1">
+        <f>IF(B42="","",ROUND(E42*F42,2))</f>
+        <v/>
+      </c>
+      <c r="H42" s="1">
+        <f>IF(B42="","",D42*G42)</f>
+        <v/>
+      </c>
       <c r="I42" s="1" t="n"/>
       <c r="J42" s="1" t="n"/>
       <c r="K42" s="1" t="n"/>
@@ -2277,12 +2431,24 @@
     <row r="43" ht="12.75" customHeight="1" s="85">
       <c r="A43" s="1" t="n"/>
       <c r="B43" s="91" t="n"/>
-      <c r="C43" s="91" t="n"/>
+      <c r="C43" s="91">
+        <f>IF(B43="","","Sale")</f>
+        <v/>
+      </c>
       <c r="D43" s="1" t="n"/>
       <c r="E43" s="1" t="n"/>
-      <c r="F43" s="1" t="n"/>
-      <c r="G43" s="1" t="n"/>
-      <c r="H43" s="1" t="n"/>
+      <c r="F43" s="1">
+        <f>IFERROR(VLOOKUP(B43,aux_ptax_historical_data!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="G43" s="1">
+        <f>IF(B43="","",ROUND(E43*F43,2))</f>
+        <v/>
+      </c>
+      <c r="H43" s="1">
+        <f>IF(B43="","",D43*G43)</f>
+        <v/>
+      </c>
       <c r="I43" s="1" t="n"/>
       <c r="J43" s="1" t="n"/>
       <c r="K43" s="1" t="n"/>
@@ -2305,12 +2471,24 @@
     <row r="44" ht="12.75" customHeight="1" s="85">
       <c r="A44" s="1" t="n"/>
       <c r="B44" s="91" t="n"/>
-      <c r="C44" s="91" t="n"/>
+      <c r="C44" s="91">
+        <f>IF(B44="","","Sale")</f>
+        <v/>
+      </c>
       <c r="D44" s="1" t="n"/>
       <c r="E44" s="1" t="n"/>
-      <c r="F44" s="1" t="n"/>
-      <c r="G44" s="1" t="n"/>
-      <c r="H44" s="1" t="n"/>
+      <c r="F44" s="1">
+        <f>IFERROR(VLOOKUP(B44,aux_ptax_historical_data!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="G44" s="1">
+        <f>IF(B44="","",ROUND(E44*F44,2))</f>
+        <v/>
+      </c>
+      <c r="H44" s="1">
+        <f>IF(B44="","",D44*G44)</f>
+        <v/>
+      </c>
       <c r="I44" s="1" t="n"/>
       <c r="J44" s="1" t="n"/>
       <c r="K44" s="1" t="n"/>
@@ -2333,12 +2511,24 @@
     <row r="45" ht="12.75" customHeight="1" s="85">
       <c r="A45" s="1" t="n"/>
       <c r="B45" s="91" t="n"/>
-      <c r="C45" s="91" t="n"/>
+      <c r="C45" s="91">
+        <f>IF(B45="","","Sale")</f>
+        <v/>
+      </c>
       <c r="D45" s="1" t="n"/>
       <c r="E45" s="1" t="n"/>
-      <c r="F45" s="1" t="n"/>
-      <c r="G45" s="1" t="n"/>
-      <c r="H45" s="1" t="n"/>
+      <c r="F45" s="1">
+        <f>IFERROR(VLOOKUP(B45,aux_ptax_historical_data!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="G45" s="1">
+        <f>IF(B45="","",ROUND(E45*F45,2))</f>
+        <v/>
+      </c>
+      <c r="H45" s="1">
+        <f>IF(B45="","",D45*G45)</f>
+        <v/>
+      </c>
       <c r="I45" s="1" t="n"/>
       <c r="J45" s="1" t="n"/>
       <c r="K45" s="1" t="n"/>
@@ -2360,13 +2550,25 @@
     </row>
     <row r="46" ht="12.75" customHeight="1" s="85">
       <c r="A46" s="1" t="n"/>
-      <c r="B46" s="1" t="n"/>
-      <c r="C46" s="1" t="n"/>
+      <c r="B46" s="91" t="n"/>
+      <c r="C46" s="1">
+        <f>IF(B46="","","Sale")</f>
+        <v/>
+      </c>
       <c r="D46" s="1" t="n"/>
       <c r="E46" s="1" t="n"/>
-      <c r="F46" s="1" t="n"/>
-      <c r="G46" s="1" t="n"/>
-      <c r="H46" s="1" t="n"/>
+      <c r="F46" s="1">
+        <f>IFERROR(VLOOKUP(B46,aux_ptax_historical_data!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="G46" s="1">
+        <f>IF(B46="","",ROUND(E46*F46,2))</f>
+        <v/>
+      </c>
+      <c r="H46" s="1">
+        <f>IF(B46="","",D46*G46)</f>
+        <v/>
+      </c>
       <c r="I46" s="1" t="n"/>
       <c r="J46" s="1" t="n"/>
       <c r="K46" s="1" t="n"/>
@@ -2388,13 +2590,25 @@
     </row>
     <row r="47" ht="12.75" customHeight="1" s="85">
       <c r="A47" s="1" t="n"/>
-      <c r="B47" s="1" t="n"/>
-      <c r="C47" s="1" t="n"/>
+      <c r="B47" s="91" t="n"/>
+      <c r="C47" s="1">
+        <f>IF(B47="","","Sale")</f>
+        <v/>
+      </c>
       <c r="D47" s="1" t="n"/>
       <c r="E47" s="1" t="n"/>
-      <c r="F47" s="1" t="n"/>
-      <c r="G47" s="1" t="n"/>
-      <c r="H47" s="1" t="n"/>
+      <c r="F47" s="1">
+        <f>IFERROR(VLOOKUP(B47,aux_ptax_historical_data!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="G47" s="1">
+        <f>IF(B47="","",ROUND(E47*F47,2))</f>
+        <v/>
+      </c>
+      <c r="H47" s="1">
+        <f>IF(B47="","",D47*G47)</f>
+        <v/>
+      </c>
       <c r="I47" s="1" t="n"/>
       <c r="J47" s="1" t="n"/>
       <c r="K47" s="1" t="n"/>
@@ -2416,13 +2630,25 @@
     </row>
     <row r="48" ht="12.75" customHeight="1" s="85">
       <c r="A48" s="1" t="n"/>
-      <c r="B48" s="1" t="n"/>
-      <c r="C48" s="1" t="n"/>
+      <c r="B48" s="91" t="n"/>
+      <c r="C48" s="1">
+        <f>IF(B48="","","Sale")</f>
+        <v/>
+      </c>
       <c r="D48" s="1" t="n"/>
       <c r="E48" s="1" t="n"/>
-      <c r="F48" s="1" t="n"/>
-      <c r="G48" s="1" t="n"/>
-      <c r="H48" s="1" t="n"/>
+      <c r="F48" s="1">
+        <f>IFERROR(VLOOKUP(B48,aux_ptax_historical_data!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="G48" s="1">
+        <f>IF(B48="","",ROUND(E48*F48,2))</f>
+        <v/>
+      </c>
+      <c r="H48" s="1">
+        <f>IF(B48="","",D48*G48)</f>
+        <v/>
+      </c>
       <c r="I48" s="1" t="n"/>
       <c r="J48" s="1" t="n"/>
       <c r="K48" s="1" t="n"/>
@@ -2472,13 +2698,23 @@
     </row>
     <row r="50" ht="12.75" customHeight="1" s="85">
       <c r="A50" s="1" t="n"/>
-      <c r="B50" s="1" t="n"/>
+      <c r="B50" s="1" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
       <c r="C50" s="1" t="n"/>
-      <c r="D50" s="1" t="n"/>
+      <c r="D50" s="1">
+        <f>SUM(D37:D48)</f>
+        <v/>
+      </c>
       <c r="E50" s="1" t="n"/>
       <c r="F50" s="1" t="n"/>
       <c r="G50" s="1" t="n"/>
-      <c r="H50" s="1" t="n"/>
+      <c r="H50" s="1">
+        <f>SUM(H37:H48)</f>
+        <v/>
+      </c>
       <c r="I50" s="1" t="n"/>
       <c r="J50" s="1" t="n"/>
       <c r="K50" s="1" t="n"/>
@@ -8201,12 +8437,6 @@
     <row r="999" ht="15.75" customHeight="1" s="85"/>
     <row r="1000" ht="15.75" customHeight="1" s="85"/>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B14:H14"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -8248,38 +8478,21 @@
           <t>Cálculo de ganho/perda de capital (se aplicável)</t>
         </is>
       </c>
-      <c r="C2" s="86" t="n"/>
-      <c r="D2" s="86" t="n"/>
-      <c r="E2" s="86" t="n"/>
-      <c r="F2" s="86" t="n"/>
-      <c r="G2" s="86" t="n"/>
-      <c r="H2" s="86" t="n"/>
-      <c r="I2" s="86" t="n"/>
-      <c r="J2" s="86" t="n"/>
       <c r="K2" s="90" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="L2" s="86" t="n"/>
-      <c r="M2" s="86" t="n"/>
-      <c r="N2" s="88" t="n"/>
       <c r="O2" s="48" t="inlineStr">
         <is>
           <t>amount_brl</t>
         </is>
       </c>
-      <c r="P2" s="86" t="n"/>
-      <c r="Q2" s="86" t="n"/>
-      <c r="R2" s="88" t="n"/>
       <c r="S2" s="48" t="inlineStr">
         <is>
           <t>amount_usd</t>
         </is>
       </c>
-      <c r="T2" s="86" t="n"/>
-      <c r="U2" s="86" t="n"/>
-      <c r="V2" s="88" t="n"/>
       <c r="W2" s="43" t="n"/>
       <c r="X2" s="43" t="n"/>
       <c r="Y2" s="43" t="n"/>
@@ -8299,99 +8512,75 @@
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>quantity_vested_sold</t>
+          <t>award_date</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>vesting_sale_price_usd</t>
+          <t>award_number</t>
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>fx_rate_brl_usd</t>
+          <t>qty</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>share_value_brl</t>
+          <t>price_usd</t>
         </is>
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>total_value_brl</t>
+          <t>fx_rate</t>
         </is>
       </c>
       <c r="I3" s="8" t="inlineStr">
         <is>
-          <t>avg_price_to_date_brl</t>
+          <t>value_usd</t>
         </is>
       </c>
       <c r="J3" s="8" t="inlineStr">
         <is>
-          <t>gain_loss_brl</t>
+          <t>value_brl</t>
         </is>
       </c>
       <c r="K3" s="48" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>run_quantity</t>
         </is>
       </c>
       <c r="L3" s="49" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>avg_cost_brl</t>
         </is>
       </c>
       <c r="M3" s="49" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>avg_cost_usd</t>
         </is>
       </c>
       <c r="N3" s="49" t="inlineStr">
         <is>
-          <t>net</t>
+          <t>pool_brl</t>
         </is>
       </c>
       <c r="O3" s="48" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>pool_usd</t>
         </is>
       </c>
       <c r="P3" s="49" t="inlineStr">
         <is>
-          <t>in</t>
-        </is>
-      </c>
-      <c r="Q3" s="49" t="inlineStr">
-        <is>
-          <t>out</t>
-        </is>
-      </c>
-      <c r="R3" s="49" t="inlineStr">
-        <is>
-          <t>net</t>
-        </is>
-      </c>
-      <c r="S3" s="48" t="inlineStr">
-        <is>
-          <t>initial</t>
-        </is>
-      </c>
-      <c r="T3" s="49" t="inlineStr">
-        <is>
-          <t>in</t>
-        </is>
-      </c>
-      <c r="U3" s="49" t="inlineStr">
-        <is>
-          <t>out</t>
-        </is>
-      </c>
-      <c r="V3" s="49" t="inlineStr">
-        <is>
-          <t>net</t>
-        </is>
-      </c>
+          <t>gain_brl</t>
+        </is>
+      </c>
+      <c r="Q3" s="49" t="n"/>
+      <c r="R3" s="49" t="n"/>
+      <c r="S3" s="48" t="n"/>
+      <c r="T3" s="49" t="n"/>
+      <c r="U3" s="49" t="n"/>
+      <c r="V3" s="49" t="n"/>
       <c r="W3" s="43" t="n"/>
       <c r="X3" s="43" t="n"/>
       <c r="Y3" s="43" t="n"/>
@@ -8399,1158 +8588,1720 @@
     </row>
     <row r="4" ht="12.75" customHeight="1" s="85">
       <c r="B4" s="50">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("SORT(FILTER(
-  { input!B8:E11;
-    input!B16:E25 },
-  { input!E8:E11;
-    input!E16:E25 } &lt;&gt; 0
-))"),45660.0)</f>
-        <v/>
-      </c>
-      <c r="C4" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Vesting")</f>
-        <v/>
-      </c>
+        <f>SORT(FILTER({ {input!B8:B31,input!C8:C31,input!D8:D31,input!E8:E31,input!F8:F31,input!G8:G31} ; {input!B37:B48,input!C37:C48,IF(input!B37:B48="","",""),IF(input!B37:B48="","",""),input!D37:D48,input!E37:E48} }, {input!F8:F31;input!D37:D48}&lt;&gt;""), 1, TRUE)</f>
+        <v/>
+      </c>
+      <c r="C4" s="10" t="n"/>
       <c r="D4" s="51" t="n"/>
-      <c r="E4" s="52">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.63)</f>
-        <v/>
-      </c>
-      <c r="F4" s="53">
-        <f>IFERROR(VLOOKUP(B4,aux_ptax_historical_data!$B:$E,4,0),"")</f>
-        <v/>
-      </c>
-      <c r="G4" s="54">
-        <f>IFERROR(E4*F4,"")</f>
-        <v/>
-      </c>
+      <c r="E4" s="52" t="n"/>
+      <c r="F4" s="53" t="n"/>
+      <c r="G4" s="54" t="n"/>
       <c r="H4" s="54">
-        <f>IFERROR(G4*D4,"")</f>
+        <f>IF($B4="","",IF($C4="Vesting",IFERROR(VLOOKUP($B4,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B4,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
         <v/>
       </c>
       <c r="I4" s="54">
-        <f>IFERROR(O4/K4,0)</f>
+        <f>IF($B4="","",$F4*$G4)</f>
         <v/>
       </c>
       <c r="J4" s="54">
-        <f>IFERROR(IF(C4="Vesting",0,H4-Q4),0)</f>
+        <f>IF($B4="","",ROUND($G4*$H4,2)*$F4)</f>
         <v/>
       </c>
       <c r="K4" s="55">
-        <f>input!$D$4</f>
+        <f>IF($B4="","",input!$D$4+IF($C4="Vesting",$F4,0)-IF($C4="Sale",$F4,0))</f>
         <v/>
       </c>
       <c r="L4" s="55">
-        <f>IF(C4="Vesting",D4,0)</f>
+        <f>IF($B4="","",IFERROR(input!$F$4/input!$D$4,0))</f>
         <v/>
       </c>
       <c r="M4" s="55">
-        <f>IF(C4="Venda",D4,0)</f>
+        <f>IF($B4="","",IFERROR(input!$H$4/input!$D$4,0))</f>
         <v/>
       </c>
       <c r="N4" s="55">
-        <f>K4+L4-M4</f>
+        <f>IF($B4="","",input!$F$4+IF($C4="Vesting",$J4,0)-IF($C4="Sale",L4*$F4,0))</f>
         <v/>
       </c>
       <c r="O4" s="54">
-        <f>input!$F$4</f>
+        <f>IF($B4="","",input!$H$4+IF($C4="Vesting",$I4,0)-IF($C4="Sale",M4*$F4,0))</f>
         <v/>
       </c>
       <c r="P4" s="54">
-        <f>IF(C4="Vesting",H4,0)</f>
-        <v/>
-      </c>
-      <c r="Q4" s="54">
-        <f>IF(C4="Venda",O4*M4/K4,0)</f>
-        <v/>
-      </c>
-      <c r="R4" s="54">
-        <f>O4+P4-Q4</f>
-        <v/>
-      </c>
-      <c r="S4" s="56">
-        <f>input!$H$4</f>
-        <v/>
-      </c>
-      <c r="T4" s="56">
-        <f>IF(C4="Vesting",D4*E4,0)</f>
-        <v/>
-      </c>
-      <c r="U4" s="56">
-        <f>IF(C4="Venda",S4*M4/K4,0)</f>
-        <v/>
-      </c>
-      <c r="V4" s="56">
-        <f>S4+T4-U4</f>
-        <v/>
-      </c>
+        <f>IF($B4="","",IF($C4="Sale",$J4-L4*$F4,0))</f>
+        <v/>
+      </c>
+      <c r="Q4" s="54" t="n"/>
+      <c r="R4" s="54" t="n"/>
+      <c r="S4" s="56" t="n"/>
+      <c r="T4" s="56" t="n"/>
+      <c r="U4" s="56" t="n"/>
+      <c r="V4" s="56" t="n"/>
     </row>
     <row r="5" ht="12.75" customHeight="1" s="85">
-      <c r="B5" s="50">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45748.0)</f>
-        <v/>
-      </c>
-      <c r="C5" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Vesting")</f>
-        <v/>
-      </c>
+      <c r="B5" s="50" t="n"/>
+      <c r="C5" s="10" t="n"/>
       <c r="D5" s="51" t="n"/>
-      <c r="E5" s="52">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.43)</f>
-        <v/>
-      </c>
-      <c r="F5" s="53">
-        <f>IFERROR(VLOOKUP(B5,aux_ptax_historical_data!$B:$E,4,0),"")</f>
-        <v/>
-      </c>
-      <c r="G5" s="54">
-        <f>IFERROR(E5*F5,"")</f>
-        <v/>
-      </c>
+      <c r="E5" s="52" t="n"/>
+      <c r="F5" s="53" t="n"/>
+      <c r="G5" s="54" t="n"/>
       <c r="H5" s="54">
-        <f>IFERROR(G5*D5,"")</f>
+        <f>IF($B5="","",IF($C5="Vesting",IFERROR(VLOOKUP($B5,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B5,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
         <v/>
       </c>
       <c r="I5" s="54">
-        <f>IFERROR(O5/K5,0)</f>
+        <f>IF($B5="","",$F5*$G5)</f>
         <v/>
       </c>
       <c r="J5" s="54">
-        <f>IFERROR(IF(C5="Vesting",0,H5-Q5),0)</f>
+        <f>IF($B5="","",ROUND($G5*$H5,2)*$F5)</f>
         <v/>
       </c>
       <c r="K5" s="55">
-        <f>K4+L4-M4</f>
+        <f>IF($B5="","",K4+IF($C5="Vesting",$F5,0)-IF($C5="Sale",$F5,0))</f>
         <v/>
       </c>
       <c r="L5" s="55">
-        <f>IF(C5="Vesting",D5,0)</f>
+        <f>IF($B5="","",IFERROR(N4/K4,0))</f>
         <v/>
       </c>
       <c r="M5" s="55">
-        <f>IF(C5="Venda",D5,0)</f>
+        <f>IF($B5="","",IFERROR(O4/K4,0))</f>
         <v/>
       </c>
       <c r="N5" s="55">
-        <f>K5+L5-M5</f>
+        <f>IF($B5="","",N4+IF($C5="Vesting",$J5,0)-IF($C5="Sale",L5*$F5,0))</f>
         <v/>
       </c>
       <c r="O5" s="54">
-        <f>R4</f>
+        <f>IF($B5="","",O4+IF($C5="Vesting",$I5,0)-IF($C5="Sale",M5*$F5,0))</f>
         <v/>
       </c>
       <c r="P5" s="54">
-        <f>IF(C5="Vesting",H5,0)</f>
-        <v/>
-      </c>
-      <c r="Q5" s="54">
-        <f>IF(C5="Venda",O5*M5/K5,0)</f>
-        <v/>
-      </c>
-      <c r="R5" s="54">
-        <f>O5+P5-Q5</f>
-        <v/>
-      </c>
-      <c r="S5" s="56">
-        <f>V4</f>
-        <v/>
-      </c>
-      <c r="T5" s="56">
-        <f>IF(C5="Vesting",D5*E5,0)</f>
-        <v/>
-      </c>
-      <c r="U5" s="56">
-        <f>IF(C5="Venda",S5*M5/K5,0)</f>
-        <v/>
-      </c>
-      <c r="V5" s="56">
-        <f>S5+T5-U5</f>
-        <v/>
-      </c>
+        <f>IF($B5="","",IF($C5="Sale",$J5-L5*$F5,0))</f>
+        <v/>
+      </c>
+      <c r="Q5" s="54" t="n"/>
+      <c r="R5" s="54" t="n"/>
+      <c r="S5" s="56" t="n"/>
+      <c r="T5" s="56" t="n"/>
+      <c r="U5" s="56" t="n"/>
+      <c r="V5" s="56" t="n"/>
     </row>
     <row r="6" ht="12.75" customHeight="1" s="85">
-      <c r="B6" s="50">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45839.0)</f>
-        <v/>
-      </c>
-      <c r="C6" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Vesting")</f>
-        <v/>
-      </c>
+      <c r="B6" s="50" t="n"/>
+      <c r="C6" s="10" t="n"/>
       <c r="D6" s="51" t="n"/>
-      <c r="E6" s="52">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.64)</f>
-        <v/>
-      </c>
-      <c r="F6" s="53">
-        <f>IFERROR(VLOOKUP(B6,aux_ptax_historical_data!$B:$E,4,0),"")</f>
-        <v/>
-      </c>
-      <c r="G6" s="54">
-        <f>IFERROR(E6*F6,"")</f>
-        <v/>
-      </c>
+      <c r="E6" s="52" t="n"/>
+      <c r="F6" s="53" t="n"/>
+      <c r="G6" s="54" t="n"/>
       <c r="H6" s="54">
-        <f>IFERROR(G6*D6,"")</f>
+        <f>IF($B6="","",IF($C6="Vesting",IFERROR(VLOOKUP($B6,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B6,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
         <v/>
       </c>
       <c r="I6" s="54">
-        <f>IFERROR(O6/K6,0)</f>
+        <f>IF($B6="","",$F6*$G6)</f>
         <v/>
       </c>
       <c r="J6" s="54">
-        <f>IFERROR(IF(C6="Vesting",0,H6-Q6),0)</f>
+        <f>IF($B6="","",ROUND($G6*$H6,2)*$F6)</f>
         <v/>
       </c>
       <c r="K6" s="55">
-        <f>K5+L5-M5</f>
+        <f>IF($B6="","",K5+IF($C6="Vesting",$F6,0)-IF($C6="Sale",$F6,0))</f>
         <v/>
       </c>
       <c r="L6" s="55">
-        <f>IF(C6="Vesting",D6,0)</f>
+        <f>IF($B6="","",IFERROR(N5/K5,0))</f>
         <v/>
       </c>
       <c r="M6" s="55">
-        <f>IF(C6="Venda",D6,0)</f>
+        <f>IF($B6="","",IFERROR(O5/K5,0))</f>
         <v/>
       </c>
       <c r="N6" s="55">
-        <f>K6+L6-M6</f>
+        <f>IF($B6="","",N5+IF($C6="Vesting",$J6,0)-IF($C6="Sale",L6*$F6,0))</f>
         <v/>
       </c>
       <c r="O6" s="54">
-        <f>R5</f>
+        <f>IF($B6="","",O5+IF($C6="Vesting",$I6,0)-IF($C6="Sale",M6*$F6,0))</f>
         <v/>
       </c>
       <c r="P6" s="54">
-        <f>IF(C6="Vesting",H6,0)</f>
-        <v/>
-      </c>
-      <c r="Q6" s="54">
-        <f>IF(C6="Venda",O6*M6/K6,0)</f>
-        <v/>
-      </c>
-      <c r="R6" s="54">
-        <f>O6+P6-Q6</f>
-        <v/>
-      </c>
-      <c r="S6" s="56">
-        <f>V5</f>
-        <v/>
-      </c>
-      <c r="T6" s="56">
-        <f>IF(C6="Vesting",D6*E6,0)</f>
-        <v/>
-      </c>
-      <c r="U6" s="56">
-        <f>IF(C6="Venda",S6*M6/K6,0)</f>
-        <v/>
-      </c>
-      <c r="V6" s="56">
-        <f>S6+T6-U6</f>
-        <v/>
-      </c>
+        <f>IF($B6="","",IF($C6="Sale",$J6-L6*$F6,0))</f>
+        <v/>
+      </c>
+      <c r="Q6" s="54" t="n"/>
+      <c r="R6" s="54" t="n"/>
+      <c r="S6" s="56" t="n"/>
+      <c r="T6" s="56" t="n"/>
+      <c r="U6" s="56" t="n"/>
+      <c r="V6" s="56" t="n"/>
     </row>
     <row r="7" ht="12.75" customHeight="1" s="85">
-      <c r="B7" s="50">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45931.0)</f>
-        <v/>
-      </c>
-      <c r="C7" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Vesting")</f>
-        <v/>
-      </c>
+      <c r="B7" s="50" t="n"/>
+      <c r="C7" s="10" t="n"/>
       <c r="D7" s="51" t="n"/>
-      <c r="E7" s="52">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.19)</f>
-        <v/>
-      </c>
-      <c r="F7" s="53">
-        <f>IFERROR(VLOOKUP(B7,aux_ptax_historical_data!$B:$E,4,0),"")</f>
-        <v/>
-      </c>
-      <c r="G7" s="54">
-        <f>IFERROR(E7*F7,"")</f>
-        <v/>
-      </c>
+      <c r="E7" s="52" t="n"/>
+      <c r="F7" s="53" t="n"/>
+      <c r="G7" s="54" t="n"/>
       <c r="H7" s="54">
-        <f>IFERROR(G7*D7,"")</f>
+        <f>IF($B7="","",IF($C7="Vesting",IFERROR(VLOOKUP($B7,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B7,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
         <v/>
       </c>
       <c r="I7" s="54">
-        <f>IFERROR(O7/K7,0)</f>
+        <f>IF($B7="","",$F7*$G7)</f>
         <v/>
       </c>
       <c r="J7" s="54">
-        <f>IFERROR(IF(C7="Vesting",0,H7-Q7),0)</f>
+        <f>IF($B7="","",ROUND($G7*$H7,2)*$F7)</f>
         <v/>
       </c>
       <c r="K7" s="55">
-        <f>K6+L6-M6</f>
+        <f>IF($B7="","",K6+IF($C7="Vesting",$F7,0)-IF($C7="Sale",$F7,0))</f>
         <v/>
       </c>
       <c r="L7" s="55">
-        <f>IF(C7="Vesting",D7,0)</f>
+        <f>IF($B7="","",IFERROR(N6/K6,0))</f>
         <v/>
       </c>
       <c r="M7" s="55">
-        <f>IF(C7="Venda",D7,0)</f>
+        <f>IF($B7="","",IFERROR(O6/K6,0))</f>
         <v/>
       </c>
       <c r="N7" s="55">
-        <f>K7+L7-M7</f>
+        <f>IF($B7="","",N6+IF($C7="Vesting",$J7,0)-IF($C7="Sale",L7*$F7,0))</f>
         <v/>
       </c>
       <c r="O7" s="54">
-        <f>R6</f>
+        <f>IF($B7="","",O6+IF($C7="Vesting",$I7,0)-IF($C7="Sale",M7*$F7,0))</f>
         <v/>
       </c>
       <c r="P7" s="54">
-        <f>IF(C7="Vesting",H7,0)</f>
-        <v/>
-      </c>
-      <c r="Q7" s="54">
-        <f>IF(C7="Venda",O7*M7/K7,0)</f>
-        <v/>
-      </c>
-      <c r="R7" s="54">
-        <f>O7+P7-Q7</f>
-        <v/>
-      </c>
-      <c r="S7" s="56">
-        <f>V6</f>
-        <v/>
-      </c>
-      <c r="T7" s="56">
-        <f>IF(C7="Vesting",D7*E7,0)</f>
-        <v/>
-      </c>
-      <c r="U7" s="56">
-        <f>IF(C7="Venda",S7*M7/K7,0)</f>
-        <v/>
-      </c>
-      <c r="V7" s="56">
-        <f>S7+T7-U7</f>
-        <v/>
-      </c>
+        <f>IF($B7="","",IF($C7="Sale",$J7-L7*$F7,0))</f>
+        <v/>
+      </c>
+      <c r="Q7" s="54" t="n"/>
+      <c r="R7" s="54" t="n"/>
+      <c r="S7" s="56" t="n"/>
+      <c r="T7" s="56" t="n"/>
+      <c r="U7" s="56" t="n"/>
+      <c r="V7" s="56" t="n"/>
     </row>
     <row r="8" ht="12.75" customHeight="1" s="85">
       <c r="B8" s="50" t="n"/>
       <c r="C8" s="10" t="n"/>
       <c r="D8" s="51" t="n"/>
       <c r="E8" s="52" t="n"/>
-      <c r="F8" s="53">
-        <f>IFERROR(VLOOKUP(B8,aux_ptax_historical_data!$B:$E,4,0),"")</f>
-        <v/>
-      </c>
-      <c r="G8" s="54">
-        <f>IFERROR(E8*F8,"")</f>
-        <v/>
-      </c>
+      <c r="F8" s="53" t="n"/>
+      <c r="G8" s="54" t="n"/>
       <c r="H8" s="54">
-        <f>IFERROR(G8*D8,"")</f>
+        <f>IF($B8="","",IF($C8="Vesting",IFERROR(VLOOKUP($B8,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B8,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
         <v/>
       </c>
       <c r="I8" s="54">
-        <f>IFERROR(O8/K8,0)</f>
+        <f>IF($B8="","",$F8*$G8)</f>
         <v/>
       </c>
       <c r="J8" s="54">
-        <f>IFERROR(IF(C8="Vesting",0,H8-Q8),0)</f>
+        <f>IF($B8="","",ROUND($G8*$H8,2)*$F8)</f>
         <v/>
       </c>
       <c r="K8" s="55">
-        <f>K7+L7-M7</f>
+        <f>IF($B8="","",K7+IF($C8="Vesting",$F8,0)-IF($C8="Sale",$F8,0))</f>
         <v/>
       </c>
       <c r="L8" s="55">
-        <f>IF(C8="Vesting",D8,0)</f>
+        <f>IF($B8="","",IFERROR(N7/K7,0))</f>
         <v/>
       </c>
       <c r="M8" s="55">
-        <f>IF(C8="Venda",D8,0)</f>
+        <f>IF($B8="","",IFERROR(O7/K7,0))</f>
         <v/>
       </c>
       <c r="N8" s="55">
-        <f>K8+L8-M8</f>
+        <f>IF($B8="","",N7+IF($C8="Vesting",$J8,0)-IF($C8="Sale",L8*$F8,0))</f>
         <v/>
       </c>
       <c r="O8" s="54">
-        <f>R7</f>
+        <f>IF($B8="","",O7+IF($C8="Vesting",$I8,0)-IF($C8="Sale",M8*$F8,0))</f>
         <v/>
       </c>
       <c r="P8" s="54">
-        <f>IF(C8="Vesting",H8,0)</f>
-        <v/>
-      </c>
-      <c r="Q8" s="54">
-        <f>IF(C8="Venda",O8*M8/K8,0)</f>
-        <v/>
-      </c>
-      <c r="R8" s="54">
-        <f>O8+P8-Q8</f>
-        <v/>
-      </c>
-      <c r="S8" s="56">
-        <f>V7</f>
-        <v/>
-      </c>
-      <c r="T8" s="56">
-        <f>IF(C8="Vesting",D8*E8,0)</f>
-        <v/>
-      </c>
-      <c r="U8" s="56">
-        <f>IF(C8="Venda",S8*M8/K8,0)</f>
-        <v/>
-      </c>
-      <c r="V8" s="56">
-        <f>S8+T8-U8</f>
-        <v/>
-      </c>
+        <f>IF($B8="","",IF($C8="Sale",$J8-L8*$F8,0))</f>
+        <v/>
+      </c>
+      <c r="Q8" s="54" t="n"/>
+      <c r="R8" s="54" t="n"/>
+      <c r="S8" s="56" t="n"/>
+      <c r="T8" s="56" t="n"/>
+      <c r="U8" s="56" t="n"/>
+      <c r="V8" s="56" t="n"/>
     </row>
     <row r="9" ht="12.75" customHeight="1" s="85">
       <c r="B9" s="50" t="n"/>
       <c r="C9" s="10" t="n"/>
       <c r="D9" s="51" t="n"/>
       <c r="E9" s="52" t="n"/>
-      <c r="F9" s="53">
-        <f>IFERROR(VLOOKUP(B9,aux_ptax_historical_data!$B:$E,4,0),"")</f>
-        <v/>
-      </c>
-      <c r="G9" s="54">
-        <f>IFERROR(E9*F9,"")</f>
-        <v/>
-      </c>
+      <c r="F9" s="53" t="n"/>
+      <c r="G9" s="54" t="n"/>
       <c r="H9" s="54">
-        <f>IFERROR(G9*D9,"")</f>
+        <f>IF($B9="","",IF($C9="Vesting",IFERROR(VLOOKUP($B9,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B9,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
         <v/>
       </c>
       <c r="I9" s="54">
-        <f>IFERROR(O9/K9,0)</f>
+        <f>IF($B9="","",$F9*$G9)</f>
         <v/>
       </c>
       <c r="J9" s="54">
-        <f>IFERROR(IF(C9="Vesting",0,H9-Q9),0)</f>
+        <f>IF($B9="","",ROUND($G9*$H9,2)*$F9)</f>
         <v/>
       </c>
       <c r="K9" s="55">
-        <f>K8+L8-M8</f>
+        <f>IF($B9="","",K8+IF($C9="Vesting",$F9,0)-IF($C9="Sale",$F9,0))</f>
         <v/>
       </c>
       <c r="L9" s="55">
-        <f>IF(C9="Vesting",D9,0)</f>
+        <f>IF($B9="","",IFERROR(N8/K8,0))</f>
         <v/>
       </c>
       <c r="M9" s="55">
-        <f>IF(C9="Venda",D9,0)</f>
+        <f>IF($B9="","",IFERROR(O8/K8,0))</f>
         <v/>
       </c>
       <c r="N9" s="55">
-        <f>K9+L9-M9</f>
+        <f>IF($B9="","",N8+IF($C9="Vesting",$J9,0)-IF($C9="Sale",L9*$F9,0))</f>
         <v/>
       </c>
       <c r="O9" s="54">
-        <f>R8</f>
+        <f>IF($B9="","",O8+IF($C9="Vesting",$I9,0)-IF($C9="Sale",M9*$F9,0))</f>
         <v/>
       </c>
       <c r="P9" s="54">
-        <f>IF(C9="Vesting",H9,0)</f>
-        <v/>
-      </c>
-      <c r="Q9" s="54">
-        <f>IF(C9="Venda",O9*M9/K9,0)</f>
-        <v/>
-      </c>
-      <c r="R9" s="54">
-        <f>O9+P9-Q9</f>
-        <v/>
-      </c>
-      <c r="S9" s="56">
-        <f>V8</f>
-        <v/>
-      </c>
-      <c r="T9" s="56">
-        <f>IF(C9="Vesting",D9*E9,0)</f>
-        <v/>
-      </c>
-      <c r="U9" s="56">
-        <f>IF(C9="Venda",S9*M9/K9,0)</f>
-        <v/>
-      </c>
-      <c r="V9" s="56">
-        <f>S9+T9-U9</f>
-        <v/>
-      </c>
+        <f>IF($B9="","",IF($C9="Sale",$J9-L9*$F9,0))</f>
+        <v/>
+      </c>
+      <c r="Q9" s="54" t="n"/>
+      <c r="R9" s="54" t="n"/>
+      <c r="S9" s="56" t="n"/>
+      <c r="T9" s="56" t="n"/>
+      <c r="U9" s="56" t="n"/>
+      <c r="V9" s="56" t="n"/>
     </row>
     <row r="10" ht="12.75" customHeight="1" s="85">
       <c r="B10" s="50" t="n"/>
       <c r="C10" s="10" t="n"/>
       <c r="D10" s="51" t="n"/>
       <c r="E10" s="52" t="n"/>
-      <c r="F10" s="53">
-        <f>IFERROR(VLOOKUP(B10,aux_ptax_historical_data!$B:$E,4,0),"")</f>
-        <v/>
-      </c>
-      <c r="G10" s="54">
-        <f>IFERROR(E10*F10,"")</f>
-        <v/>
-      </c>
+      <c r="F10" s="53" t="n"/>
+      <c r="G10" s="54" t="n"/>
       <c r="H10" s="54">
-        <f>IFERROR(G10*D10,"")</f>
+        <f>IF($B10="","",IF($C10="Vesting",IFERROR(VLOOKUP($B10,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B10,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
         <v/>
       </c>
       <c r="I10" s="54">
-        <f>IFERROR(O10/K10,0)</f>
+        <f>IF($B10="","",$F10*$G10)</f>
         <v/>
       </c>
       <c r="J10" s="54">
-        <f>IFERROR(IF(C10="Vesting",0,H10-Q10),0)</f>
+        <f>IF($B10="","",ROUND($G10*$H10,2)*$F10)</f>
         <v/>
       </c>
       <c r="K10" s="55">
-        <f>K9+L9-M9</f>
+        <f>IF($B10="","",K9+IF($C10="Vesting",$F10,0)-IF($C10="Sale",$F10,0))</f>
         <v/>
       </c>
       <c r="L10" s="55">
-        <f>IF(C10="Vesting",D10,0)</f>
+        <f>IF($B10="","",IFERROR(N9/K9,0))</f>
         <v/>
       </c>
       <c r="M10" s="55">
-        <f>IF(C10="Venda",D10,0)</f>
+        <f>IF($B10="","",IFERROR(O9/K9,0))</f>
         <v/>
       </c>
       <c r="N10" s="55">
-        <f>K10+L10-M10</f>
+        <f>IF($B10="","",N9+IF($C10="Vesting",$J10,0)-IF($C10="Sale",L10*$F10,0))</f>
         <v/>
       </c>
       <c r="O10" s="54">
-        <f>R9</f>
+        <f>IF($B10="","",O9+IF($C10="Vesting",$I10,0)-IF($C10="Sale",M10*$F10,0))</f>
         <v/>
       </c>
       <c r="P10" s="54">
-        <f>IF(C10="Vesting",H10,0)</f>
-        <v/>
-      </c>
-      <c r="Q10" s="54">
-        <f>IF(C10="Venda",O10*M10/K10,0)</f>
-        <v/>
-      </c>
-      <c r="R10" s="54">
-        <f>O10+P10-Q10</f>
-        <v/>
-      </c>
-      <c r="S10" s="56">
-        <f>V9</f>
-        <v/>
-      </c>
-      <c r="T10" s="56">
-        <f>IF(C10="Vesting",D10*E10,0)</f>
-        <v/>
-      </c>
-      <c r="U10" s="56">
-        <f>IF(C10="Venda",S10*M10/K10,0)</f>
-        <v/>
-      </c>
-      <c r="V10" s="56">
-        <f>S10+T10-U10</f>
-        <v/>
-      </c>
+        <f>IF($B10="","",IF($C10="Sale",$J10-L10*$F10,0))</f>
+        <v/>
+      </c>
+      <c r="Q10" s="54" t="n"/>
+      <c r="R10" s="54" t="n"/>
+      <c r="S10" s="56" t="n"/>
+      <c r="T10" s="56" t="n"/>
+      <c r="U10" s="56" t="n"/>
+      <c r="V10" s="56" t="n"/>
     </row>
     <row r="11" ht="12.75" customHeight="1" s="85">
       <c r="B11" s="50" t="n"/>
       <c r="C11" s="10" t="n"/>
       <c r="D11" s="51" t="n"/>
       <c r="E11" s="52" t="n"/>
-      <c r="F11" s="53">
-        <f>IFERROR(VLOOKUP(B11,aux_ptax_historical_data!$B:$E,4,0),"")</f>
-        <v/>
-      </c>
-      <c r="G11" s="54">
-        <f>IFERROR(E11*F11,"")</f>
-        <v/>
-      </c>
+      <c r="F11" s="53" t="n"/>
+      <c r="G11" s="54" t="n"/>
       <c r="H11" s="54">
-        <f>IFERROR(G11*D11,"")</f>
+        <f>IF($B11="","",IF($C11="Vesting",IFERROR(VLOOKUP($B11,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B11,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
         <v/>
       </c>
       <c r="I11" s="54">
-        <f>IFERROR(O11/K11,0)</f>
+        <f>IF($B11="","",$F11*$G11)</f>
         <v/>
       </c>
       <c r="J11" s="54">
-        <f>IFERROR(IF(C11="Vesting",0,H11-Q11),0)</f>
+        <f>IF($B11="","",ROUND($G11*$H11,2)*$F11)</f>
         <v/>
       </c>
       <c r="K11" s="55">
-        <f>K10+L10-M10</f>
+        <f>IF($B11="","",K10+IF($C11="Vesting",$F11,0)-IF($C11="Sale",$F11,0))</f>
         <v/>
       </c>
       <c r="L11" s="55">
-        <f>IF(C11="Vesting",D11,0)</f>
+        <f>IF($B11="","",IFERROR(N10/K10,0))</f>
         <v/>
       </c>
       <c r="M11" s="55">
-        <f>IF(C11="Venda",D11,0)</f>
+        <f>IF($B11="","",IFERROR(O10/K10,0))</f>
         <v/>
       </c>
       <c r="N11" s="55">
-        <f>K11+L11-M11</f>
+        <f>IF($B11="","",N10+IF($C11="Vesting",$J11,0)-IF($C11="Sale",L11*$F11,0))</f>
         <v/>
       </c>
       <c r="O11" s="54">
-        <f>R10</f>
+        <f>IF($B11="","",O10+IF($C11="Vesting",$I11,0)-IF($C11="Sale",M11*$F11,0))</f>
         <v/>
       </c>
       <c r="P11" s="54">
-        <f>IF(C11="Vesting",H11,0)</f>
-        <v/>
-      </c>
-      <c r="Q11" s="54">
-        <f>IF(C11="Venda",O11*M11/K11,0)</f>
-        <v/>
-      </c>
-      <c r="R11" s="54">
-        <f>O11+P11-Q11</f>
-        <v/>
-      </c>
-      <c r="S11" s="56">
-        <f>V10</f>
-        <v/>
-      </c>
-      <c r="T11" s="56">
-        <f>IF(C11="Vesting",D11*E11,0)</f>
-        <v/>
-      </c>
-      <c r="U11" s="56">
-        <f>IF(C11="Venda",S11*M11/K11,0)</f>
-        <v/>
-      </c>
-      <c r="V11" s="56">
-        <f>S11+T11-U11</f>
-        <v/>
-      </c>
+        <f>IF($B11="","",IF($C11="Sale",$J11-L11*$F11,0))</f>
+        <v/>
+      </c>
+      <c r="Q11" s="54" t="n"/>
+      <c r="R11" s="54" t="n"/>
+      <c r="S11" s="56" t="n"/>
+      <c r="T11" s="56" t="n"/>
+      <c r="U11" s="56" t="n"/>
+      <c r="V11" s="56" t="n"/>
     </row>
     <row r="12" ht="12.75" customHeight="1" s="85">
       <c r="B12" s="50" t="n"/>
       <c r="C12" s="10" t="n"/>
       <c r="D12" s="51" t="n"/>
       <c r="E12" s="52" t="n"/>
-      <c r="F12" s="53">
-        <f>IFERROR(VLOOKUP(B12,aux_ptax_historical_data!$B:$E,4,0),"")</f>
-        <v/>
-      </c>
-      <c r="G12" s="54">
-        <f>IFERROR(E12*F12,"")</f>
-        <v/>
-      </c>
+      <c r="F12" s="53" t="n"/>
+      <c r="G12" s="54" t="n"/>
       <c r="H12" s="54">
-        <f>IFERROR(G12*D12,"")</f>
+        <f>IF($B12="","",IF($C12="Vesting",IFERROR(VLOOKUP($B12,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B12,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
         <v/>
       </c>
       <c r="I12" s="54">
-        <f>IFERROR(O12/K12,0)</f>
+        <f>IF($B12="","",$F12*$G12)</f>
         <v/>
       </c>
       <c r="J12" s="54">
-        <f>IFERROR(IF(C12="Vesting",0,H12-Q12),0)</f>
+        <f>IF($B12="","",ROUND($G12*$H12,2)*$F12)</f>
         <v/>
       </c>
       <c r="K12" s="55">
-        <f>K11+L11-M11</f>
+        <f>IF($B12="","",K11+IF($C12="Vesting",$F12,0)-IF($C12="Sale",$F12,0))</f>
         <v/>
       </c>
       <c r="L12" s="55">
-        <f>IF(C12="Vesting",D12,0)</f>
+        <f>IF($B12="","",IFERROR(N11/K11,0))</f>
         <v/>
       </c>
       <c r="M12" s="55">
-        <f>IF(C12="Venda",D12,0)</f>
+        <f>IF($B12="","",IFERROR(O11/K11,0))</f>
         <v/>
       </c>
       <c r="N12" s="55">
-        <f>K12+L12-M12</f>
+        <f>IF($B12="","",N11+IF($C12="Vesting",$J12,0)-IF($C12="Sale",L12*$F12,0))</f>
         <v/>
       </c>
       <c r="O12" s="54">
-        <f>R11</f>
+        <f>IF($B12="","",O11+IF($C12="Vesting",$I12,0)-IF($C12="Sale",M12*$F12,0))</f>
         <v/>
       </c>
       <c r="P12" s="54">
-        <f>IF(C12="Vesting",H12,0)</f>
-        <v/>
-      </c>
-      <c r="Q12" s="54">
-        <f>IF(C12="Venda",O12*M12/K12,0)</f>
-        <v/>
-      </c>
-      <c r="R12" s="54">
-        <f>O12+P12-Q12</f>
-        <v/>
-      </c>
-      <c r="S12" s="56">
-        <f>V11</f>
-        <v/>
-      </c>
-      <c r="T12" s="56">
-        <f>IF(C12="Vesting",D12*E12,0)</f>
-        <v/>
-      </c>
-      <c r="U12" s="56">
-        <f>IF(C12="Venda",S12*M12/K12,0)</f>
-        <v/>
-      </c>
-      <c r="V12" s="56">
-        <f>S12+T12-U12</f>
-        <v/>
-      </c>
+        <f>IF($B12="","",IF($C12="Sale",$J12-L12*$F12,0))</f>
+        <v/>
+      </c>
+      <c r="Q12" s="54" t="n"/>
+      <c r="R12" s="54" t="n"/>
+      <c r="S12" s="56" t="n"/>
+      <c r="T12" s="56" t="n"/>
+      <c r="U12" s="56" t="n"/>
+      <c r="V12" s="56" t="n"/>
     </row>
     <row r="13" ht="12.75" customHeight="1" s="85">
       <c r="B13" s="50" t="n"/>
       <c r="C13" s="10" t="n"/>
       <c r="D13" s="51" t="n"/>
       <c r="E13" s="52" t="n"/>
-      <c r="F13" s="53">
-        <f>IFERROR(VLOOKUP(B13,aux_ptax_historical_data!$B:$E,4,0),"")</f>
-        <v/>
-      </c>
-      <c r="G13" s="54">
-        <f>IFERROR(E13*F13,"")</f>
-        <v/>
-      </c>
+      <c r="F13" s="53" t="n"/>
+      <c r="G13" s="54" t="n"/>
       <c r="H13" s="54">
-        <f>IFERROR(G13*D13,"")</f>
+        <f>IF($B13="","",IF($C13="Vesting",IFERROR(VLOOKUP($B13,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B13,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
         <v/>
       </c>
       <c r="I13" s="54">
-        <f>IFERROR(O13/K13,0)</f>
+        <f>IF($B13="","",$F13*$G13)</f>
         <v/>
       </c>
       <c r="J13" s="54">
-        <f>IFERROR(IF(C13="Vesting",0,H13-Q13),0)</f>
+        <f>IF($B13="","",ROUND($G13*$H13,2)*$F13)</f>
         <v/>
       </c>
       <c r="K13" s="55">
-        <f>K12+L12-M12</f>
+        <f>IF($B13="","",K12+IF($C13="Vesting",$F13,0)-IF($C13="Sale",$F13,0))</f>
         <v/>
       </c>
       <c r="L13" s="55">
-        <f>IF(C13="Vesting",D13,0)</f>
+        <f>IF($B13="","",IFERROR(N12/K12,0))</f>
         <v/>
       </c>
       <c r="M13" s="55">
-        <f>IF(C13="Venda",D13,0)</f>
+        <f>IF($B13="","",IFERROR(O12/K12,0))</f>
         <v/>
       </c>
       <c r="N13" s="55">
-        <f>K13+L13-M13</f>
+        <f>IF($B13="","",N12+IF($C13="Vesting",$J13,0)-IF($C13="Sale",L13*$F13,0))</f>
         <v/>
       </c>
       <c r="O13" s="54">
-        <f>R12</f>
+        <f>IF($B13="","",O12+IF($C13="Vesting",$I13,0)-IF($C13="Sale",M13*$F13,0))</f>
         <v/>
       </c>
       <c r="P13" s="54">
-        <f>IF(C13="Vesting",H13,0)</f>
-        <v/>
-      </c>
-      <c r="Q13" s="54">
-        <f>IF(C13="Venda",O13*M13/K13,0)</f>
-        <v/>
-      </c>
-      <c r="R13" s="54">
-        <f>O13+P13-Q13</f>
-        <v/>
-      </c>
-      <c r="S13" s="56">
-        <f>V12</f>
-        <v/>
-      </c>
-      <c r="T13" s="56">
-        <f>IF(C13="Vesting",D13*E13,0)</f>
-        <v/>
-      </c>
-      <c r="U13" s="56">
-        <f>IF(C13="Venda",S13*M13/K13,0)</f>
-        <v/>
-      </c>
-      <c r="V13" s="56">
-        <f>S13+T13-U13</f>
-        <v/>
-      </c>
+        <f>IF($B13="","",IF($C13="Sale",$J13-L13*$F13,0))</f>
+        <v/>
+      </c>
+      <c r="Q13" s="54" t="n"/>
+      <c r="R13" s="54" t="n"/>
+      <c r="S13" s="56" t="n"/>
+      <c r="T13" s="56" t="n"/>
+      <c r="U13" s="56" t="n"/>
+      <c r="V13" s="56" t="n"/>
     </row>
     <row r="14" ht="12.75" customHeight="1" s="85">
       <c r="B14" s="50" t="n"/>
       <c r="C14" s="10" t="n"/>
       <c r="D14" s="51" t="n"/>
       <c r="E14" s="52" t="n"/>
-      <c r="F14" s="53">
-        <f>IFERROR(VLOOKUP(B14,aux_ptax_historical_data!$B:$E,4,0),"")</f>
-        <v/>
-      </c>
-      <c r="G14" s="54">
-        <f>IFERROR(E14*F14,"")</f>
-        <v/>
-      </c>
+      <c r="F14" s="53" t="n"/>
+      <c r="G14" s="54" t="n"/>
       <c r="H14" s="54">
-        <f>IFERROR(G14*D14,"")</f>
+        <f>IF($B14="","",IF($C14="Vesting",IFERROR(VLOOKUP($B14,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B14,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
         <v/>
       </c>
       <c r="I14" s="54">
-        <f>IFERROR(O14/K14,0)</f>
+        <f>IF($B14="","",$F14*$G14)</f>
         <v/>
       </c>
       <c r="J14" s="54">
-        <f>IFERROR(IF(C14="Vesting",0,H14-Q14),0)</f>
+        <f>IF($B14="","",ROUND($G14*$H14,2)*$F14)</f>
         <v/>
       </c>
       <c r="K14" s="55">
-        <f>K13+L13-M13</f>
+        <f>IF($B14="","",K13+IF($C14="Vesting",$F14,0)-IF($C14="Sale",$F14,0))</f>
         <v/>
       </c>
       <c r="L14" s="55">
-        <f>IF(C14="Vesting",D14,0)</f>
+        <f>IF($B14="","",IFERROR(N13/K13,0))</f>
         <v/>
       </c>
       <c r="M14" s="55">
-        <f>IF(C14="Venda",D14,0)</f>
+        <f>IF($B14="","",IFERROR(O13/K13,0))</f>
         <v/>
       </c>
       <c r="N14" s="55">
-        <f>K14+L14-M14</f>
+        <f>IF($B14="","",N13+IF($C14="Vesting",$J14,0)-IF($C14="Sale",L14*$F14,0))</f>
         <v/>
       </c>
       <c r="O14" s="54">
-        <f>R13</f>
+        <f>IF($B14="","",O13+IF($C14="Vesting",$I14,0)-IF($C14="Sale",M14*$F14,0))</f>
         <v/>
       </c>
       <c r="P14" s="54">
-        <f>IF(C14="Vesting",H14,0)</f>
-        <v/>
-      </c>
-      <c r="Q14" s="54">
-        <f>IF(C14="Venda",O14*M14/K14,0)</f>
-        <v/>
-      </c>
-      <c r="R14" s="54">
-        <f>O14+P14-Q14</f>
-        <v/>
-      </c>
-      <c r="S14" s="56">
-        <f>V13</f>
-        <v/>
-      </c>
-      <c r="T14" s="56">
-        <f>IF(C14="Vesting",D14*E14,0)</f>
-        <v/>
-      </c>
-      <c r="U14" s="56">
-        <f>IF(C14="Venda",S14*M14/K14,0)</f>
-        <v/>
-      </c>
-      <c r="V14" s="56">
-        <f>S14+T14-U14</f>
-        <v/>
-      </c>
+        <f>IF($B14="","",IF($C14="Sale",$J14-L14*$F14,0))</f>
+        <v/>
+      </c>
+      <c r="Q14" s="54" t="n"/>
+      <c r="R14" s="54" t="n"/>
+      <c r="S14" s="56" t="n"/>
+      <c r="T14" s="56" t="n"/>
+      <c r="U14" s="56" t="n"/>
+      <c r="V14" s="56" t="n"/>
     </row>
     <row r="15" ht="12.75" customHeight="1" s="85">
       <c r="B15" s="57" t="n"/>
-      <c r="C15" s="58" t="inlineStr"/>
+      <c r="C15" s="58" t="n"/>
       <c r="D15" s="59" t="n"/>
       <c r="E15" s="60" t="n"/>
-      <c r="F15" s="61">
-        <f>IFERROR(VLOOKUP(B15,aux_ptax_historical_data!$B:$E,4,0),"")</f>
-        <v/>
-      </c>
-      <c r="G15" s="54">
-        <f>IFERROR(E15*F15,"")</f>
-        <v/>
-      </c>
+      <c r="F15" s="61" t="n"/>
+      <c r="G15" s="54" t="n"/>
       <c r="H15" s="54">
-        <f>IFERROR(G15*D15,"")</f>
+        <f>IF($B15="","",IF($C15="Vesting",IFERROR(VLOOKUP($B15,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B15,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
         <v/>
       </c>
       <c r="I15" s="54">
-        <f>IFERROR(O15/K15,0)</f>
+        <f>IF($B15="","",$F15*$G15)</f>
         <v/>
       </c>
       <c r="J15" s="54">
-        <f>IFERROR(IF(C15="Vesting",0,H15-Q15),0)</f>
+        <f>IF($B15="","",ROUND($G15*$H15,2)*$F15)</f>
         <v/>
       </c>
       <c r="K15" s="55">
-        <f>K14+L14-M14</f>
+        <f>IF($B15="","",K14+IF($C15="Vesting",$F15,0)-IF($C15="Sale",$F15,0))</f>
         <v/>
       </c>
       <c r="L15" s="55">
-        <f>IF(C15="Vesting",D15,0)</f>
+        <f>IF($B15="","",IFERROR(N14/K14,0))</f>
         <v/>
       </c>
       <c r="M15" s="55">
-        <f>IF(C15="Venda",D15,0)</f>
+        <f>IF($B15="","",IFERROR(O14/K14,0))</f>
         <v/>
       </c>
       <c r="N15" s="55">
-        <f>K15+L15-M15</f>
+        <f>IF($B15="","",N14+IF($C15="Vesting",$J15,0)-IF($C15="Sale",L15*$F15,0))</f>
         <v/>
       </c>
       <c r="O15" s="54">
-        <f>R14</f>
+        <f>IF($B15="","",O14+IF($C15="Vesting",$I15,0)-IF($C15="Sale",M15*$F15,0))</f>
         <v/>
       </c>
       <c r="P15" s="54">
-        <f>IF(C15="Vesting",H15,0)</f>
-        <v/>
-      </c>
-      <c r="Q15" s="54">
-        <f>IF(C15="Venda",O15*M15/K15,0)</f>
-        <v/>
-      </c>
-      <c r="R15" s="54">
-        <f>O15+P15-Q15</f>
-        <v/>
-      </c>
-      <c r="S15" s="56">
-        <f>V14</f>
-        <v/>
-      </c>
-      <c r="T15" s="56">
-        <f>IF(C15="Vesting",D15*E15,0)</f>
-        <v/>
-      </c>
-      <c r="U15" s="56">
-        <f>IF(C15="Venda",S15*M15/K15,0)</f>
-        <v/>
-      </c>
-      <c r="V15" s="56">
-        <f>S15+T15-U15</f>
-        <v/>
-      </c>
+        <f>IF($B15="","",IF($C15="Sale",$J15-L15*$F15,0))</f>
+        <v/>
+      </c>
+      <c r="Q15" s="54" t="n"/>
+      <c r="R15" s="54" t="n"/>
+      <c r="S15" s="56" t="n"/>
+      <c r="T15" s="56" t="n"/>
+      <c r="U15" s="56" t="n"/>
+      <c r="V15" s="56" t="n"/>
     </row>
     <row r="16" ht="12.75" customHeight="1" s="85">
       <c r="B16" s="57" t="n"/>
-      <c r="C16" s="58" t="inlineStr"/>
+      <c r="C16" s="58" t="n"/>
       <c r="D16" s="59" t="n"/>
       <c r="E16" s="60" t="n"/>
-      <c r="F16" s="61">
-        <f>IFERROR(VLOOKUP(B16,aux_ptax_historical_data!$B:$E,4,0),"")</f>
-        <v/>
-      </c>
-      <c r="G16" s="54">
-        <f>IFERROR(E16*F16,"")</f>
-        <v/>
-      </c>
+      <c r="F16" s="61" t="n"/>
+      <c r="G16" s="54" t="n"/>
       <c r="H16" s="54">
-        <f>IFERROR(G16*D16,"")</f>
+        <f>IF($B16="","",IF($C16="Vesting",IFERROR(VLOOKUP($B16,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B16,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
         <v/>
       </c>
       <c r="I16" s="54">
-        <f>IFERROR(O16/K16,0)</f>
+        <f>IF($B16="","",$F16*$G16)</f>
         <v/>
       </c>
       <c r="J16" s="54">
-        <f>IFERROR(IF(C16="Vesting",0,H16-Q16),0)</f>
+        <f>IF($B16="","",ROUND($G16*$H16,2)*$F16)</f>
         <v/>
       </c>
       <c r="K16" s="55">
-        <f>K15+L15-M15</f>
+        <f>IF($B16="","",K15+IF($C16="Vesting",$F16,0)-IF($C16="Sale",$F16,0))</f>
         <v/>
       </c>
       <c r="L16" s="55">
-        <f>IF(C16="Vesting",D16,0)</f>
+        <f>IF($B16="","",IFERROR(N15/K15,0))</f>
         <v/>
       </c>
       <c r="M16" s="55">
-        <f>IF(C16="Venda",D16,0)</f>
+        <f>IF($B16="","",IFERROR(O15/K15,0))</f>
         <v/>
       </c>
       <c r="N16" s="55">
-        <f>K16+L16-M16</f>
+        <f>IF($B16="","",N15+IF($C16="Vesting",$J16,0)-IF($C16="Sale",L16*$F16,0))</f>
         <v/>
       </c>
       <c r="O16" s="54">
-        <f>R15</f>
+        <f>IF($B16="","",O15+IF($C16="Vesting",$I16,0)-IF($C16="Sale",M16*$F16,0))</f>
         <v/>
       </c>
       <c r="P16" s="54">
-        <f>IF(C16="Vesting",H16,0)</f>
-        <v/>
-      </c>
-      <c r="Q16" s="54">
-        <f>IF(C16="Venda",O16*M16/K16,0)</f>
-        <v/>
-      </c>
-      <c r="R16" s="54">
-        <f>O16+P16-Q16</f>
-        <v/>
-      </c>
-      <c r="S16" s="56">
-        <f>V15</f>
-        <v/>
-      </c>
-      <c r="T16" s="56">
-        <f>IF(C16="Vesting",D16*E16,0)</f>
-        <v/>
-      </c>
-      <c r="U16" s="56">
-        <f>IF(C16="Venda",S16*M16/K16,0)</f>
-        <v/>
-      </c>
-      <c r="V16" s="56">
-        <f>S16+T16-U16</f>
-        <v/>
-      </c>
+        <f>IF($B16="","",IF($C16="Sale",$J16-L16*$F16,0))</f>
+        <v/>
+      </c>
+      <c r="Q16" s="54" t="n"/>
+      <c r="R16" s="54" t="n"/>
+      <c r="S16" s="56" t="n"/>
+      <c r="T16" s="56" t="n"/>
+      <c r="U16" s="56" t="n"/>
+      <c r="V16" s="56" t="n"/>
     </row>
     <row r="17" ht="12.75" customHeight="1" s="85">
       <c r="B17" s="57" t="n"/>
-      <c r="C17" s="58" t="inlineStr"/>
+      <c r="C17" s="58" t="n"/>
       <c r="D17" s="59" t="n"/>
       <c r="E17" s="60" t="n"/>
-      <c r="F17" s="61">
-        <f>IFERROR(VLOOKUP(B17,aux_ptax_historical_data!$B:$E,4,0),"")</f>
-        <v/>
-      </c>
-      <c r="G17" s="54">
-        <f>IFERROR(E17*F17,"")</f>
-        <v/>
-      </c>
+      <c r="F17" s="61" t="n"/>
+      <c r="G17" s="54" t="n"/>
       <c r="H17" s="54">
-        <f>IFERROR(G17*D17,"")</f>
+        <f>IF($B17="","",IF($C17="Vesting",IFERROR(VLOOKUP($B17,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B17,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
         <v/>
       </c>
       <c r="I17" s="54">
-        <f>IFERROR(O17/K17,0)</f>
+        <f>IF($B17="","",$F17*$G17)</f>
         <v/>
       </c>
       <c r="J17" s="54">
-        <f>IFERROR(IF(C17="Vesting",0,H17-Q17),0)</f>
+        <f>IF($B17="","",ROUND($G17*$H17,2)*$F17)</f>
         <v/>
       </c>
       <c r="K17" s="55">
-        <f>K16+L16-M16</f>
+        <f>IF($B17="","",K16+IF($C17="Vesting",$F17,0)-IF($C17="Sale",$F17,0))</f>
         <v/>
       </c>
       <c r="L17" s="55">
-        <f>IF(C17="Vesting",D17,0)</f>
+        <f>IF($B17="","",IFERROR(N16/K16,0))</f>
         <v/>
       </c>
       <c r="M17" s="55">
-        <f>IF(C17="Venda",D17,0)</f>
+        <f>IF($B17="","",IFERROR(O16/K16,0))</f>
         <v/>
       </c>
       <c r="N17" s="55">
-        <f>K17+L17-M17</f>
+        <f>IF($B17="","",N16+IF($C17="Vesting",$J17,0)-IF($C17="Sale",L17*$F17,0))</f>
         <v/>
       </c>
       <c r="O17" s="54">
-        <f>R16</f>
+        <f>IF($B17="","",O16+IF($C17="Vesting",$I17,0)-IF($C17="Sale",M17*$F17,0))</f>
         <v/>
       </c>
       <c r="P17" s="54">
-        <f>IF(C17="Vesting",H17,0)</f>
-        <v/>
-      </c>
-      <c r="Q17" s="54">
-        <f>IF(C17="Venda",O17*M17/K17,0)</f>
-        <v/>
-      </c>
-      <c r="R17" s="54">
-        <f>O17+P17-Q17</f>
-        <v/>
-      </c>
-      <c r="S17" s="56">
-        <f>V16</f>
-        <v/>
-      </c>
-      <c r="T17" s="56">
-        <f>IF(C17="Vesting",D17*E17,0)</f>
-        <v/>
-      </c>
-      <c r="U17" s="56">
-        <f>IF(C17="Venda",S17*M17/K17,0)</f>
-        <v/>
-      </c>
-      <c r="V17" s="56">
-        <f>S17+T17-U17</f>
-        <v/>
-      </c>
+        <f>IF($B17="","",IF($C17="Sale",$J17-L17*$F17,0))</f>
+        <v/>
+      </c>
+      <c r="Q17" s="54" t="n"/>
+      <c r="R17" s="54" t="n"/>
+      <c r="S17" s="56" t="n"/>
+      <c r="T17" s="56" t="n"/>
+      <c r="U17" s="56" t="n"/>
+      <c r="V17" s="56" t="n"/>
     </row>
     <row r="18" ht="12.75" customHeight="1" s="85">
       <c r="B18" s="42" t="n"/>
+      <c r="H18">
+        <f>IF($B18="","",IF($C18="Vesting",IFERROR(VLOOKUP($B18,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B18,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
+        <v/>
+      </c>
+      <c r="I18">
+        <f>IF($B18="","",$F18*$G18)</f>
+        <v/>
+      </c>
+      <c r="J18">
+        <f>IF($B18="","",ROUND($G18*$H18,2)*$F18)</f>
+        <v/>
+      </c>
+      <c r="K18">
+        <f>IF($B18="","",K17+IF($C18="Vesting",$F18,0)-IF($C18="Sale",$F18,0))</f>
+        <v/>
+      </c>
+      <c r="L18">
+        <f>IF($B18="","",IFERROR(N17/K17,0))</f>
+        <v/>
+      </c>
+      <c r="M18">
+        <f>IF($B18="","",IFERROR(O17/K17,0))</f>
+        <v/>
+      </c>
+      <c r="N18">
+        <f>IF($B18="","",N17+IF($C18="Vesting",$J18,0)-IF($C18="Sale",L18*$F18,0))</f>
+        <v/>
+      </c>
+      <c r="O18">
+        <f>IF($B18="","",O17+IF($C18="Vesting",$I18,0)-IF($C18="Sale",M18*$F18,0))</f>
+        <v/>
+      </c>
+      <c r="P18">
+        <f>IF($B18="","",IF($C18="Sale",$J18-L18*$F18,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="19" ht="12.75" customHeight="1" s="85">
       <c r="B19" s="42" t="n"/>
+      <c r="H19">
+        <f>IF($B19="","",IF($C19="Vesting",IFERROR(VLOOKUP($B19,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B19,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
+        <v/>
+      </c>
+      <c r="I19">
+        <f>IF($B19="","",$F19*$G19)</f>
+        <v/>
+      </c>
+      <c r="J19">
+        <f>IF($B19="","",ROUND($G19*$H19,2)*$F19)</f>
+        <v/>
+      </c>
+      <c r="K19">
+        <f>IF($B19="","",K18+IF($C19="Vesting",$F19,0)-IF($C19="Sale",$F19,0))</f>
+        <v/>
+      </c>
+      <c r="L19">
+        <f>IF($B19="","",IFERROR(N18/K18,0))</f>
+        <v/>
+      </c>
+      <c r="M19">
+        <f>IF($B19="","",IFERROR(O18/K18,0))</f>
+        <v/>
+      </c>
+      <c r="N19">
+        <f>IF($B19="","",N18+IF($C19="Vesting",$J19,0)-IF($C19="Sale",L19*$F19,0))</f>
+        <v/>
+      </c>
+      <c r="O19">
+        <f>IF($B19="","",O18+IF($C19="Vesting",$I19,0)-IF($C19="Sale",M19*$F19,0))</f>
+        <v/>
+      </c>
+      <c r="P19">
+        <f>IF($B19="","",IF($C19="Sale",$J19-L19*$F19,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="20" ht="12.75" customHeight="1" s="85">
       <c r="B20" s="42" t="n"/>
+      <c r="H20">
+        <f>IF($B20="","",IF($C20="Vesting",IFERROR(VLOOKUP($B20,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B20,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
+        <v/>
+      </c>
+      <c r="I20">
+        <f>IF($B20="","",$F20*$G20)</f>
+        <v/>
+      </c>
+      <c r="J20">
+        <f>IF($B20="","",ROUND($G20*$H20,2)*$F20)</f>
+        <v/>
+      </c>
+      <c r="K20">
+        <f>IF($B20="","",K19+IF($C20="Vesting",$F20,0)-IF($C20="Sale",$F20,0))</f>
+        <v/>
+      </c>
+      <c r="L20">
+        <f>IF($B20="","",IFERROR(N19/K19,0))</f>
+        <v/>
+      </c>
+      <c r="M20">
+        <f>IF($B20="","",IFERROR(O19/K19,0))</f>
+        <v/>
+      </c>
+      <c r="N20">
+        <f>IF($B20="","",N19+IF($C20="Vesting",$J20,0)-IF($C20="Sale",L20*$F20,0))</f>
+        <v/>
+      </c>
+      <c r="O20">
+        <f>IF($B20="","",O19+IF($C20="Vesting",$I20,0)-IF($C20="Sale",M20*$F20,0))</f>
+        <v/>
+      </c>
+      <c r="P20">
+        <f>IF($B20="","",IF($C20="Sale",$J20-L20*$F20,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="21" ht="12.75" customHeight="1" s="85">
       <c r="B21" s="42" t="n"/>
+      <c r="H21">
+        <f>IF($B21="","",IF($C21="Vesting",IFERROR(VLOOKUP($B21,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B21,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
+        <v/>
+      </c>
+      <c r="I21">
+        <f>IF($B21="","",$F21*$G21)</f>
+        <v/>
+      </c>
+      <c r="J21">
+        <f>IF($B21="","",ROUND($G21*$H21,2)*$F21)</f>
+        <v/>
+      </c>
+      <c r="K21">
+        <f>IF($B21="","",K20+IF($C21="Vesting",$F21,0)-IF($C21="Sale",$F21,0))</f>
+        <v/>
+      </c>
+      <c r="L21">
+        <f>IF($B21="","",IFERROR(N20/K20,0))</f>
+        <v/>
+      </c>
+      <c r="M21">
+        <f>IF($B21="","",IFERROR(O20/K20,0))</f>
+        <v/>
+      </c>
+      <c r="N21">
+        <f>IF($B21="","",N20+IF($C21="Vesting",$J21,0)-IF($C21="Sale",L21*$F21,0))</f>
+        <v/>
+      </c>
+      <c r="O21">
+        <f>IF($B21="","",O20+IF($C21="Vesting",$I21,0)-IF($C21="Sale",M21*$F21,0))</f>
+        <v/>
+      </c>
+      <c r="P21">
+        <f>IF($B21="","",IF($C21="Sale",$J21-L21*$F21,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="22" ht="12.75" customHeight="1" s="85">
       <c r="B22" s="42" t="n"/>
+      <c r="H22">
+        <f>IF($B22="","",IF($C22="Vesting",IFERROR(VLOOKUP($B22,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B22,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
+        <v/>
+      </c>
+      <c r="I22">
+        <f>IF($B22="","",$F22*$G22)</f>
+        <v/>
+      </c>
+      <c r="J22">
+        <f>IF($B22="","",ROUND($G22*$H22,2)*$F22)</f>
+        <v/>
+      </c>
+      <c r="K22">
+        <f>IF($B22="","",K21+IF($C22="Vesting",$F22,0)-IF($C22="Sale",$F22,0))</f>
+        <v/>
+      </c>
+      <c r="L22">
+        <f>IF($B22="","",IFERROR(N21/K21,0))</f>
+        <v/>
+      </c>
+      <c r="M22">
+        <f>IF($B22="","",IFERROR(O21/K21,0))</f>
+        <v/>
+      </c>
+      <c r="N22">
+        <f>IF($B22="","",N21+IF($C22="Vesting",$J22,0)-IF($C22="Sale",L22*$F22,0))</f>
+        <v/>
+      </c>
+      <c r="O22">
+        <f>IF($B22="","",O21+IF($C22="Vesting",$I22,0)-IF($C22="Sale",M22*$F22,0))</f>
+        <v/>
+      </c>
+      <c r="P22">
+        <f>IF($B22="","",IF($C22="Sale",$J22-L22*$F22,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="23" ht="12.75" customHeight="1" s="85">
       <c r="B23" s="42" t="n"/>
+      <c r="H23">
+        <f>IF($B23="","",IF($C23="Vesting",IFERROR(VLOOKUP($B23,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B23,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
+        <v/>
+      </c>
+      <c r="I23">
+        <f>IF($B23="","",$F23*$G23)</f>
+        <v/>
+      </c>
+      <c r="J23">
+        <f>IF($B23="","",ROUND($G23*$H23,2)*$F23)</f>
+        <v/>
+      </c>
+      <c r="K23">
+        <f>IF($B23="","",K22+IF($C23="Vesting",$F23,0)-IF($C23="Sale",$F23,0))</f>
+        <v/>
+      </c>
+      <c r="L23">
+        <f>IF($B23="","",IFERROR(N22/K22,0))</f>
+        <v/>
+      </c>
+      <c r="M23">
+        <f>IF($B23="","",IFERROR(O22/K22,0))</f>
+        <v/>
+      </c>
+      <c r="N23">
+        <f>IF($B23="","",N22+IF($C23="Vesting",$J23,0)-IF($C23="Sale",L23*$F23,0))</f>
+        <v/>
+      </c>
+      <c r="O23">
+        <f>IF($B23="","",O22+IF($C23="Vesting",$I23,0)-IF($C23="Sale",M23*$F23,0))</f>
+        <v/>
+      </c>
+      <c r="P23">
+        <f>IF($B23="","",IF($C23="Sale",$J23-L23*$F23,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="24" ht="12.75" customHeight="1" s="85">
       <c r="B24" s="42" t="n"/>
+      <c r="H24">
+        <f>IF($B24="","",IF($C24="Vesting",IFERROR(VLOOKUP($B24,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B24,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
+        <v/>
+      </c>
+      <c r="I24">
+        <f>IF($B24="","",$F24*$G24)</f>
+        <v/>
+      </c>
+      <c r="J24">
+        <f>IF($B24="","",ROUND($G24*$H24,2)*$F24)</f>
+        <v/>
+      </c>
+      <c r="K24">
+        <f>IF($B24="","",K23+IF($C24="Vesting",$F24,0)-IF($C24="Sale",$F24,0))</f>
+        <v/>
+      </c>
+      <c r="L24">
+        <f>IF($B24="","",IFERROR(N23/K23,0))</f>
+        <v/>
+      </c>
+      <c r="M24">
+        <f>IF($B24="","",IFERROR(O23/K23,0))</f>
+        <v/>
+      </c>
+      <c r="N24">
+        <f>IF($B24="","",N23+IF($C24="Vesting",$J24,0)-IF($C24="Sale",L24*$F24,0))</f>
+        <v/>
+      </c>
+      <c r="O24">
+        <f>IF($B24="","",O23+IF($C24="Vesting",$I24,0)-IF($C24="Sale",M24*$F24,0))</f>
+        <v/>
+      </c>
+      <c r="P24">
+        <f>IF($B24="","",IF($C24="Sale",$J24-L24*$F24,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="25" ht="12.75" customHeight="1" s="85">
       <c r="B25" s="42" t="n"/>
+      <c r="H25">
+        <f>IF($B25="","",IF($C25="Vesting",IFERROR(VLOOKUP($B25,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B25,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
+        <v/>
+      </c>
+      <c r="I25">
+        <f>IF($B25="","",$F25*$G25)</f>
+        <v/>
+      </c>
+      <c r="J25">
+        <f>IF($B25="","",ROUND($G25*$H25,2)*$F25)</f>
+        <v/>
+      </c>
+      <c r="K25">
+        <f>IF($B25="","",K24+IF($C25="Vesting",$F25,0)-IF($C25="Sale",$F25,0))</f>
+        <v/>
+      </c>
+      <c r="L25">
+        <f>IF($B25="","",IFERROR(N24/K24,0))</f>
+        <v/>
+      </c>
+      <c r="M25">
+        <f>IF($B25="","",IFERROR(O24/K24,0))</f>
+        <v/>
+      </c>
+      <c r="N25">
+        <f>IF($B25="","",N24+IF($C25="Vesting",$J25,0)-IF($C25="Sale",L25*$F25,0))</f>
+        <v/>
+      </c>
+      <c r="O25">
+        <f>IF($B25="","",O24+IF($C25="Vesting",$I25,0)-IF($C25="Sale",M25*$F25,0))</f>
+        <v/>
+      </c>
+      <c r="P25">
+        <f>IF($B25="","",IF($C25="Sale",$J25-L25*$F25,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="26" ht="12.75" customHeight="1" s="85">
       <c r="B26" s="42" t="n"/>
+      <c r="H26">
+        <f>IF($B26="","",IF($C26="Vesting",IFERROR(VLOOKUP($B26,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B26,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
+        <v/>
+      </c>
+      <c r="I26">
+        <f>IF($B26="","",$F26*$G26)</f>
+        <v/>
+      </c>
+      <c r="J26">
+        <f>IF($B26="","",ROUND($G26*$H26,2)*$F26)</f>
+        <v/>
+      </c>
+      <c r="K26">
+        <f>IF($B26="","",K25+IF($C26="Vesting",$F26,0)-IF($C26="Sale",$F26,0))</f>
+        <v/>
+      </c>
+      <c r="L26">
+        <f>IF($B26="","",IFERROR(N25/K25,0))</f>
+        <v/>
+      </c>
+      <c r="M26">
+        <f>IF($B26="","",IFERROR(O25/K25,0))</f>
+        <v/>
+      </c>
+      <c r="N26">
+        <f>IF($B26="","",N25+IF($C26="Vesting",$J26,0)-IF($C26="Sale",L26*$F26,0))</f>
+        <v/>
+      </c>
+      <c r="O26">
+        <f>IF($B26="","",O25+IF($C26="Vesting",$I26,0)-IF($C26="Sale",M26*$F26,0))</f>
+        <v/>
+      </c>
+      <c r="P26">
+        <f>IF($B26="","",IF($C26="Sale",$J26-L26*$F26,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="27" ht="12.75" customHeight="1" s="85">
       <c r="B27" s="42" t="n"/>
+      <c r="H27">
+        <f>IF($B27="","",IF($C27="Vesting",IFERROR(VLOOKUP($B27,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B27,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
+        <v/>
+      </c>
+      <c r="I27">
+        <f>IF($B27="","",$F27*$G27)</f>
+        <v/>
+      </c>
+      <c r="J27">
+        <f>IF($B27="","",ROUND($G27*$H27,2)*$F27)</f>
+        <v/>
+      </c>
+      <c r="K27">
+        <f>IF($B27="","",K26+IF($C27="Vesting",$F27,0)-IF($C27="Sale",$F27,0))</f>
+        <v/>
+      </c>
+      <c r="L27">
+        <f>IF($B27="","",IFERROR(N26/K26,0))</f>
+        <v/>
+      </c>
+      <c r="M27">
+        <f>IF($B27="","",IFERROR(O26/K26,0))</f>
+        <v/>
+      </c>
+      <c r="N27">
+        <f>IF($B27="","",N26+IF($C27="Vesting",$J27,0)-IF($C27="Sale",L27*$F27,0))</f>
+        <v/>
+      </c>
+      <c r="O27">
+        <f>IF($B27="","",O26+IF($C27="Vesting",$I27,0)-IF($C27="Sale",M27*$F27,0))</f>
+        <v/>
+      </c>
+      <c r="P27">
+        <f>IF($B27="","",IF($C27="Sale",$J27-L27*$F27,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="28" ht="12.75" customHeight="1" s="85">
       <c r="B28" s="42" t="n"/>
+      <c r="H28">
+        <f>IF($B28="","",IF($C28="Vesting",IFERROR(VLOOKUP($B28,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B28,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
+        <v/>
+      </c>
+      <c r="I28">
+        <f>IF($B28="","",$F28*$G28)</f>
+        <v/>
+      </c>
+      <c r="J28">
+        <f>IF($B28="","",ROUND($G28*$H28,2)*$F28)</f>
+        <v/>
+      </c>
+      <c r="K28">
+        <f>IF($B28="","",K27+IF($C28="Vesting",$F28,0)-IF($C28="Sale",$F28,0))</f>
+        <v/>
+      </c>
+      <c r="L28">
+        <f>IF($B28="","",IFERROR(N27/K27,0))</f>
+        <v/>
+      </c>
+      <c r="M28">
+        <f>IF($B28="","",IFERROR(O27/K27,0))</f>
+        <v/>
+      </c>
+      <c r="N28">
+        <f>IF($B28="","",N27+IF($C28="Vesting",$J28,0)-IF($C28="Sale",L28*$F28,0))</f>
+        <v/>
+      </c>
+      <c r="O28">
+        <f>IF($B28="","",O27+IF($C28="Vesting",$I28,0)-IF($C28="Sale",M28*$F28,0))</f>
+        <v/>
+      </c>
+      <c r="P28">
+        <f>IF($B28="","",IF($C28="Sale",$J28-L28*$F28,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="29" ht="12.75" customHeight="1" s="85">
       <c r="B29" s="42" t="n"/>
+      <c r="H29">
+        <f>IF($B29="","",IF($C29="Vesting",IFERROR(VLOOKUP($B29,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B29,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
+        <v/>
+      </c>
+      <c r="I29">
+        <f>IF($B29="","",$F29*$G29)</f>
+        <v/>
+      </c>
+      <c r="J29">
+        <f>IF($B29="","",ROUND($G29*$H29,2)*$F29)</f>
+        <v/>
+      </c>
+      <c r="K29">
+        <f>IF($B29="","",K28+IF($C29="Vesting",$F29,0)-IF($C29="Sale",$F29,0))</f>
+        <v/>
+      </c>
+      <c r="L29">
+        <f>IF($B29="","",IFERROR(N28/K28,0))</f>
+        <v/>
+      </c>
+      <c r="M29">
+        <f>IF($B29="","",IFERROR(O28/K28,0))</f>
+        <v/>
+      </c>
+      <c r="N29">
+        <f>IF($B29="","",N28+IF($C29="Vesting",$J29,0)-IF($C29="Sale",L29*$F29,0))</f>
+        <v/>
+      </c>
+      <c r="O29">
+        <f>IF($B29="","",O28+IF($C29="Vesting",$I29,0)-IF($C29="Sale",M29*$F29,0))</f>
+        <v/>
+      </c>
+      <c r="P29">
+        <f>IF($B29="","",IF($C29="Sale",$J29-L29*$F29,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="30" ht="12.75" customHeight="1" s="85">
       <c r="B30" s="42" t="n"/>
+      <c r="H30">
+        <f>IF($B30="","",IF($C30="Vesting",IFERROR(VLOOKUP($B30,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B30,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
+        <v/>
+      </c>
+      <c r="I30">
+        <f>IF($B30="","",$F30*$G30)</f>
+        <v/>
+      </c>
+      <c r="J30">
+        <f>IF($B30="","",ROUND($G30*$H30,2)*$F30)</f>
+        <v/>
+      </c>
+      <c r="K30">
+        <f>IF($B30="","",K29+IF($C30="Vesting",$F30,0)-IF($C30="Sale",$F30,0))</f>
+        <v/>
+      </c>
+      <c r="L30">
+        <f>IF($B30="","",IFERROR(N29/K29,0))</f>
+        <v/>
+      </c>
+      <c r="M30">
+        <f>IF($B30="","",IFERROR(O29/K29,0))</f>
+        <v/>
+      </c>
+      <c r="N30">
+        <f>IF($B30="","",N29+IF($C30="Vesting",$J30,0)-IF($C30="Sale",L30*$F30,0))</f>
+        <v/>
+      </c>
+      <c r="O30">
+        <f>IF($B30="","",O29+IF($C30="Vesting",$I30,0)-IF($C30="Sale",M30*$F30,0))</f>
+        <v/>
+      </c>
+      <c r="P30">
+        <f>IF($B30="","",IF($C30="Sale",$J30-L30*$F30,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="31" ht="12.75" customHeight="1" s="85">
       <c r="B31" s="42" t="n"/>
+      <c r="H31">
+        <f>IF($B31="","",IF($C31="Vesting",IFERROR(VLOOKUP($B31,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B31,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
+        <v/>
+      </c>
+      <c r="I31">
+        <f>IF($B31="","",$F31*$G31)</f>
+        <v/>
+      </c>
+      <c r="J31">
+        <f>IF($B31="","",ROUND($G31*$H31,2)*$F31)</f>
+        <v/>
+      </c>
+      <c r="K31">
+        <f>IF($B31="","",K30+IF($C31="Vesting",$F31,0)-IF($C31="Sale",$F31,0))</f>
+        <v/>
+      </c>
+      <c r="L31">
+        <f>IF($B31="","",IFERROR(N30/K30,0))</f>
+        <v/>
+      </c>
+      <c r="M31">
+        <f>IF($B31="","",IFERROR(O30/K30,0))</f>
+        <v/>
+      </c>
+      <c r="N31">
+        <f>IF($B31="","",N30+IF($C31="Vesting",$J31,0)-IF($C31="Sale",L31*$F31,0))</f>
+        <v/>
+      </c>
+      <c r="O31">
+        <f>IF($B31="","",O30+IF($C31="Vesting",$I31,0)-IF($C31="Sale",M31*$F31,0))</f>
+        <v/>
+      </c>
+      <c r="P31">
+        <f>IF($B31="","",IF($C31="Sale",$J31-L31*$F31,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="32" ht="12.75" customHeight="1" s="85">
       <c r="B32" s="42" t="n"/>
+      <c r="H32">
+        <f>IF($B32="","",IF($C32="Vesting",IFERROR(VLOOKUP($B32,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B32,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
+        <v/>
+      </c>
+      <c r="I32">
+        <f>IF($B32="","",$F32*$G32)</f>
+        <v/>
+      </c>
+      <c r="J32">
+        <f>IF($B32="","",ROUND($G32*$H32,2)*$F32)</f>
+        <v/>
+      </c>
+      <c r="K32">
+        <f>IF($B32="","",K31+IF($C32="Vesting",$F32,0)-IF($C32="Sale",$F32,0))</f>
+        <v/>
+      </c>
+      <c r="L32">
+        <f>IF($B32="","",IFERROR(N31/K31,0))</f>
+        <v/>
+      </c>
+      <c r="M32">
+        <f>IF($B32="","",IFERROR(O31/K31,0))</f>
+        <v/>
+      </c>
+      <c r="N32">
+        <f>IF($B32="","",N31+IF($C32="Vesting",$J32,0)-IF($C32="Sale",L32*$F32,0))</f>
+        <v/>
+      </c>
+      <c r="O32">
+        <f>IF($B32="","",O31+IF($C32="Vesting",$I32,0)-IF($C32="Sale",M32*$F32,0))</f>
+        <v/>
+      </c>
+      <c r="P32">
+        <f>IF($B32="","",IF($C32="Sale",$J32-L32*$F32,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="33" ht="12.75" customHeight="1" s="85">
       <c r="B33" s="42" t="n"/>
+      <c r="H33">
+        <f>IF($B33="","",IF($C33="Vesting",IFERROR(VLOOKUP($B33,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B33,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
+        <v/>
+      </c>
+      <c r="I33">
+        <f>IF($B33="","",$F33*$G33)</f>
+        <v/>
+      </c>
+      <c r="J33">
+        <f>IF($B33="","",ROUND($G33*$H33,2)*$F33)</f>
+        <v/>
+      </c>
+      <c r="K33">
+        <f>IF($B33="","",K32+IF($C33="Vesting",$F33,0)-IF($C33="Sale",$F33,0))</f>
+        <v/>
+      </c>
+      <c r="L33">
+        <f>IF($B33="","",IFERROR(N32/K32,0))</f>
+        <v/>
+      </c>
+      <c r="M33">
+        <f>IF($B33="","",IFERROR(O32/K32,0))</f>
+        <v/>
+      </c>
+      <c r="N33">
+        <f>IF($B33="","",N32+IF($C33="Vesting",$J33,0)-IF($C33="Sale",L33*$F33,0))</f>
+        <v/>
+      </c>
+      <c r="O33">
+        <f>IF($B33="","",O32+IF($C33="Vesting",$I33,0)-IF($C33="Sale",M33*$F33,0))</f>
+        <v/>
+      </c>
+      <c r="P33">
+        <f>IF($B33="","",IF($C33="Sale",$J33-L33*$F33,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="34" ht="12.75" customHeight="1" s="85">
       <c r="B34" s="42" t="n"/>
+      <c r="H34">
+        <f>IF($B34="","",IF($C34="Vesting",IFERROR(VLOOKUP($B34,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B34,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
+        <v/>
+      </c>
+      <c r="I34">
+        <f>IF($B34="","",$F34*$G34)</f>
+        <v/>
+      </c>
+      <c r="J34">
+        <f>IF($B34="","",ROUND($G34*$H34,2)*$F34)</f>
+        <v/>
+      </c>
+      <c r="K34">
+        <f>IF($B34="","",K33+IF($C34="Vesting",$F34,0)-IF($C34="Sale",$F34,0))</f>
+        <v/>
+      </c>
+      <c r="L34">
+        <f>IF($B34="","",IFERROR(N33/K33,0))</f>
+        <v/>
+      </c>
+      <c r="M34">
+        <f>IF($B34="","",IFERROR(O33/K33,0))</f>
+        <v/>
+      </c>
+      <c r="N34">
+        <f>IF($B34="","",N33+IF($C34="Vesting",$J34,0)-IF($C34="Sale",L34*$F34,0))</f>
+        <v/>
+      </c>
+      <c r="O34">
+        <f>IF($B34="","",O33+IF($C34="Vesting",$I34,0)-IF($C34="Sale",M34*$F34,0))</f>
+        <v/>
+      </c>
+      <c r="P34">
+        <f>IF($B34="","",IF($C34="Sale",$J34-L34*$F34,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="35" ht="12.75" customHeight="1" s="85">
       <c r="B35" s="42" t="n"/>
+      <c r="H35">
+        <f>IF($B35="","",IF($C35="Vesting",IFERROR(VLOOKUP($B35,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B35,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
+        <v/>
+      </c>
+      <c r="I35">
+        <f>IF($B35="","",$F35*$G35)</f>
+        <v/>
+      </c>
+      <c r="J35">
+        <f>IF($B35="","",ROUND($G35*$H35,2)*$F35)</f>
+        <v/>
+      </c>
+      <c r="K35">
+        <f>IF($B35="","",K34+IF($C35="Vesting",$F35,0)-IF($C35="Sale",$F35,0))</f>
+        <v/>
+      </c>
+      <c r="L35">
+        <f>IF($B35="","",IFERROR(N34/K34,0))</f>
+        <v/>
+      </c>
+      <c r="M35">
+        <f>IF($B35="","",IFERROR(O34/K34,0))</f>
+        <v/>
+      </c>
+      <c r="N35">
+        <f>IF($B35="","",N34+IF($C35="Vesting",$J35,0)-IF($C35="Sale",L35*$F35,0))</f>
+        <v/>
+      </c>
+      <c r="O35">
+        <f>IF($B35="","",O34+IF($C35="Vesting",$I35,0)-IF($C35="Sale",M35*$F35,0))</f>
+        <v/>
+      </c>
+      <c r="P35">
+        <f>IF($B35="","",IF($C35="Sale",$J35-L35*$F35,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="36" ht="12.75" customHeight="1" s="85">
       <c r="B36" s="42" t="n"/>
+      <c r="H36">
+        <f>IF($B36="","",IF($C36="Vesting",IFERROR(VLOOKUP($B36,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B36,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
+        <v/>
+      </c>
+      <c r="I36">
+        <f>IF($B36="","",$F36*$G36)</f>
+        <v/>
+      </c>
+      <c r="J36">
+        <f>IF($B36="","",ROUND($G36*$H36,2)*$F36)</f>
+        <v/>
+      </c>
+      <c r="K36">
+        <f>IF($B36="","",K35+IF($C36="Vesting",$F36,0)-IF($C36="Sale",$F36,0))</f>
+        <v/>
+      </c>
+      <c r="L36">
+        <f>IF($B36="","",IFERROR(N35/K35,0))</f>
+        <v/>
+      </c>
+      <c r="M36">
+        <f>IF($B36="","",IFERROR(O35/K35,0))</f>
+        <v/>
+      </c>
+      <c r="N36">
+        <f>IF($B36="","",N35+IF($C36="Vesting",$J36,0)-IF($C36="Sale",L36*$F36,0))</f>
+        <v/>
+      </c>
+      <c r="O36">
+        <f>IF($B36="","",O35+IF($C36="Vesting",$I36,0)-IF($C36="Sale",M36*$F36,0))</f>
+        <v/>
+      </c>
+      <c r="P36">
+        <f>IF($B36="","",IF($C36="Sale",$J36-L36*$F36,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="37" ht="12.75" customHeight="1" s="85">
       <c r="B37" s="42" t="n"/>
+      <c r="H37">
+        <f>IF($B37="","",IF($C37="Vesting",IFERROR(VLOOKUP($B37,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B37,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
+        <v/>
+      </c>
+      <c r="I37">
+        <f>IF($B37="","",$F37*$G37)</f>
+        <v/>
+      </c>
+      <c r="J37">
+        <f>IF($B37="","",ROUND($G37*$H37,2)*$F37)</f>
+        <v/>
+      </c>
+      <c r="K37">
+        <f>IF($B37="","",K36+IF($C37="Vesting",$F37,0)-IF($C37="Sale",$F37,0))</f>
+        <v/>
+      </c>
+      <c r="L37">
+        <f>IF($B37="","",IFERROR(N36/K36,0))</f>
+        <v/>
+      </c>
+      <c r="M37">
+        <f>IF($B37="","",IFERROR(O36/K36,0))</f>
+        <v/>
+      </c>
+      <c r="N37">
+        <f>IF($B37="","",N36+IF($C37="Vesting",$J37,0)-IF($C37="Sale",L37*$F37,0))</f>
+        <v/>
+      </c>
+      <c r="O37">
+        <f>IF($B37="","",O36+IF($C37="Vesting",$I37,0)-IF($C37="Sale",M37*$F37,0))</f>
+        <v/>
+      </c>
+      <c r="P37">
+        <f>IF($B37="","",IF($C37="Sale",$J37-L37*$F37,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="38" ht="12.75" customHeight="1" s="85">
       <c r="B38" s="42" t="n"/>
+      <c r="H38">
+        <f>IF($B38="","",IF($C38="Vesting",IFERROR(VLOOKUP($B38,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B38,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
+        <v/>
+      </c>
+      <c r="I38">
+        <f>IF($B38="","",$F38*$G38)</f>
+        <v/>
+      </c>
+      <c r="J38">
+        <f>IF($B38="","",ROUND($G38*$H38,2)*$F38)</f>
+        <v/>
+      </c>
+      <c r="K38">
+        <f>IF($B38="","",K37+IF($C38="Vesting",$F38,0)-IF($C38="Sale",$F38,0))</f>
+        <v/>
+      </c>
+      <c r="L38">
+        <f>IF($B38="","",IFERROR(N37/K37,0))</f>
+        <v/>
+      </c>
+      <c r="M38">
+        <f>IF($B38="","",IFERROR(O37/K37,0))</f>
+        <v/>
+      </c>
+      <c r="N38">
+        <f>IF($B38="","",N37+IF($C38="Vesting",$J38,0)-IF($C38="Sale",L38*$F38,0))</f>
+        <v/>
+      </c>
+      <c r="O38">
+        <f>IF($B38="","",O37+IF($C38="Vesting",$I38,0)-IF($C38="Sale",M38*$F38,0))</f>
+        <v/>
+      </c>
+      <c r="P38">
+        <f>IF($B38="","",IF($C38="Sale",$J38-L38*$F38,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="39" ht="12.75" customHeight="1" s="85">
       <c r="B39" s="42" t="n"/>
+      <c r="H39">
+        <f>IF($B39="","",IF($C39="Vesting",IFERROR(VLOOKUP($B39,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B39,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
+        <v/>
+      </c>
+      <c r="I39">
+        <f>IF($B39="","",$F39*$G39)</f>
+        <v/>
+      </c>
+      <c r="J39">
+        <f>IF($B39="","",ROUND($G39*$H39,2)*$F39)</f>
+        <v/>
+      </c>
+      <c r="K39">
+        <f>IF($B39="","",K38+IF($C39="Vesting",$F39,0)-IF($C39="Sale",$F39,0))</f>
+        <v/>
+      </c>
+      <c r="L39">
+        <f>IF($B39="","",IFERROR(N38/K38,0))</f>
+        <v/>
+      </c>
+      <c r="M39">
+        <f>IF($B39="","",IFERROR(O38/K38,0))</f>
+        <v/>
+      </c>
+      <c r="N39">
+        <f>IF($B39="","",N38+IF($C39="Vesting",$J39,0)-IF($C39="Sale",L39*$F39,0))</f>
+        <v/>
+      </c>
+      <c r="O39">
+        <f>IF($B39="","",O38+IF($C39="Vesting",$I39,0)-IF($C39="Sale",M39*$F39,0))</f>
+        <v/>
+      </c>
+      <c r="P39">
+        <f>IF($B39="","",IF($C39="Sale",$J39-L39*$F39,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="40" ht="12.75" customHeight="1" s="85">
       <c r="B40" s="42" t="n"/>
+      <c r="H40">
+        <f>IF($B40="","",IF($C40="Vesting",IFERROR(VLOOKUP($B40,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B40,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
+        <v/>
+      </c>
+      <c r="I40">
+        <f>IF($B40="","",$F40*$G40)</f>
+        <v/>
+      </c>
+      <c r="J40">
+        <f>IF($B40="","",ROUND($G40*$H40,2)*$F40)</f>
+        <v/>
+      </c>
+      <c r="K40">
+        <f>IF($B40="","",K39+IF($C40="Vesting",$F40,0)-IF($C40="Sale",$F40,0))</f>
+        <v/>
+      </c>
+      <c r="L40">
+        <f>IF($B40="","",IFERROR(N39/K39,0))</f>
+        <v/>
+      </c>
+      <c r="M40">
+        <f>IF($B40="","",IFERROR(O39/K39,0))</f>
+        <v/>
+      </c>
+      <c r="N40">
+        <f>IF($B40="","",N39+IF($C40="Vesting",$J40,0)-IF($C40="Sale",L40*$F40,0))</f>
+        <v/>
+      </c>
+      <c r="O40">
+        <f>IF($B40="","",O39+IF($C40="Vesting",$I40,0)-IF($C40="Sale",M40*$F40,0))</f>
+        <v/>
+      </c>
+      <c r="P40">
+        <f>IF($B40="","",IF($C40="Sale",$J40-L40*$F40,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="41" ht="12.75" customHeight="1" s="85">
       <c r="B41" s="42" t="n"/>
+      <c r="H41">
+        <f>IF($B41="","",IF($C41="Vesting",IFERROR(VLOOKUP($B41,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B41,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
+        <v/>
+      </c>
+      <c r="I41">
+        <f>IF($B41="","",$F41*$G41)</f>
+        <v/>
+      </c>
+      <c r="J41">
+        <f>IF($B41="","",ROUND($G41*$H41,2)*$F41)</f>
+        <v/>
+      </c>
+      <c r="K41">
+        <f>IF($B41="","",K40+IF($C41="Vesting",$F41,0)-IF($C41="Sale",$F41,0))</f>
+        <v/>
+      </c>
+      <c r="L41">
+        <f>IF($B41="","",IFERROR(N40/K40,0))</f>
+        <v/>
+      </c>
+      <c r="M41">
+        <f>IF($B41="","",IFERROR(O40/K40,0))</f>
+        <v/>
+      </c>
+      <c r="N41">
+        <f>IF($B41="","",N40+IF($C41="Vesting",$J41,0)-IF($C41="Sale",L41*$F41,0))</f>
+        <v/>
+      </c>
+      <c r="O41">
+        <f>IF($B41="","",O40+IF($C41="Vesting",$I41,0)-IF($C41="Sale",M41*$F41,0))</f>
+        <v/>
+      </c>
+      <c r="P41">
+        <f>IF($B41="","",IF($C41="Sale",$J41-L41*$F41,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="42" ht="12.75" customHeight="1" s="85">
       <c r="B42" s="42" t="n"/>
+      <c r="H42">
+        <f>IF($B42="","",IF($C42="Vesting",IFERROR(VLOOKUP($B42,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B42,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
+        <v/>
+      </c>
+      <c r="I42">
+        <f>IF($B42="","",$F42*$G42)</f>
+        <v/>
+      </c>
+      <c r="J42">
+        <f>IF($B42="","",ROUND($G42*$H42,2)*$F42)</f>
+        <v/>
+      </c>
+      <c r="K42">
+        <f>IF($B42="","",K41+IF($C42="Vesting",$F42,0)-IF($C42="Sale",$F42,0))</f>
+        <v/>
+      </c>
+      <c r="L42">
+        <f>IF($B42="","",IFERROR(N41/K41,0))</f>
+        <v/>
+      </c>
+      <c r="M42">
+        <f>IF($B42="","",IFERROR(O41/K41,0))</f>
+        <v/>
+      </c>
+      <c r="N42">
+        <f>IF($B42="","",N41+IF($C42="Vesting",$J42,0)-IF($C42="Sale",L42*$F42,0))</f>
+        <v/>
+      </c>
+      <c r="O42">
+        <f>IF($B42="","",O41+IF($C42="Vesting",$I42,0)-IF($C42="Sale",M42*$F42,0))</f>
+        <v/>
+      </c>
+      <c r="P42">
+        <f>IF($B42="","",IF($C42="Sale",$J42-L42*$F42,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="43" ht="12.75" customHeight="1" s="85">
       <c r="B43" s="42" t="n"/>
+      <c r="H43">
+        <f>IF($B43="","",IF($C43="Vesting",IFERROR(VLOOKUP($B43,aux_ptax_historical_data!$B:$E,4,0),""),IFERROR(VLOOKUP($B43,aux_ptax_historical_data!$B:$E,3,0),"")))</f>
+        <v/>
+      </c>
+      <c r="I43">
+        <f>IF($B43="","",$F43*$G43)</f>
+        <v/>
+      </c>
+      <c r="J43">
+        <f>IF($B43="","",ROUND($G43*$H43,2)*$F43)</f>
+        <v/>
+      </c>
+      <c r="K43">
+        <f>IF($B43="","",K42+IF($C43="Vesting",$F43,0)-IF($C43="Sale",$F43,0))</f>
+        <v/>
+      </c>
+      <c r="L43">
+        <f>IF($B43="","",IFERROR(N42/K42,0))</f>
+        <v/>
+      </c>
+      <c r="M43">
+        <f>IF($B43="","",IFERROR(O42/K42,0))</f>
+        <v/>
+      </c>
+      <c r="N43">
+        <f>IF($B43="","",N42+IF($C43="Vesting",$J43,0)-IF($C43="Sale",L43*$F43,0))</f>
+        <v/>
+      </c>
+      <c r="O43">
+        <f>IF($B43="","",O42+IF($C43="Vesting",$I43,0)-IF($C43="Sale",M43*$F43,0))</f>
+        <v/>
+      </c>
+      <c r="P43">
+        <f>IF($B43="","",IF($C43="Sale",$J43-L43*$F43,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="44" ht="12.75" customHeight="1" s="85">
       <c r="B44" s="42" t="n"/>
@@ -12424,12 +13175,6 @@
       <c r="B1000" s="42" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="B2:J2"/>
-    <mergeCell ref="O2:R2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="S2:V2"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -38256,11 +39001,6 @@
           <t>Capital gain/loss calculation (if applicable)</t>
         </is>
       </c>
-      <c r="C2" s="86" t="n"/>
-      <c r="D2" s="86" t="n"/>
-      <c r="E2" s="86" t="n"/>
-      <c r="F2" s="86" t="n"/>
-      <c r="G2" s="86" t="n"/>
       <c r="H2" s="73" t="n"/>
       <c r="I2" s="73" t="n"/>
       <c r="J2" s="73" t="n"/>
@@ -38292,22 +39032,22 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>quantity_sold</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>quantity_sold</t>
+          <t>proceeds_brl</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>avg_price_to_date_brl</t>
+          <t>avg_cost_brl</t>
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>share_value_brl</t>
+          <t>gain_loss_brl</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
@@ -38340,29 +39080,14 @@
     <row r="4" ht="12.75" customHeight="1" s="85">
       <c r="A4" s="1" t="n"/>
       <c r="B4" s="74">
-        <f>input!B16</f>
-        <v/>
-      </c>
-      <c r="C4" s="55">
-        <f>IF(B4="","", "Cálculo")</f>
-        <v/>
-      </c>
-      <c r="D4" s="75">
-        <f>input!D16</f>
-        <v/>
-      </c>
-      <c r="E4" s="76">
-        <f t="array" ref="E4">IFERROR(INDEX(do_not_change__calculation_memo!$I$4:$I$17,MATCH(1,(do_not_change__calculation_memo!$B$4:$B$17=B4)*(do_not_change__calculation_memo!$C$4:$C$17="Venda"),0)),"")</f>
-        <v/>
-      </c>
-      <c r="F4" s="76">
-        <f>input!G16</f>
-        <v/>
-      </c>
-      <c r="G4" s="76">
-        <f>IFERROR(IF(B4="","",D4*F4-D4*E4),0)</f>
-        <v/>
-      </c>
+        <f>IFERROR(FILTER({do_not_change__calculation_memo!$B$4:$B$43,do_not_change__calculation_memo!$F$4:$F$43,do_not_change__calculation_memo!$J$4:$J$43,do_not_change__calculation_memo!$L$4:$L$43,do_not_change__calculation_memo!$P$4:$P$43},do_not_change__calculation_memo!$C$4:$C$43="Sale"),"")</f>
+        <v/>
+      </c>
+      <c r="C4" s="55" t="n"/>
+      <c r="D4" s="75" t="n"/>
+      <c r="E4" s="76" t="n"/>
+      <c r="F4" s="76" t="n"/>
+      <c r="G4" s="76" t="n"/>
       <c r="H4" s="77" t="n"/>
       <c r="I4" s="1" t="n"/>
       <c r="J4" s="1" t="n"/>
@@ -38387,30 +39112,12 @@
     </row>
     <row r="5" ht="12.75" customHeight="1" s="85">
       <c r="A5" s="1" t="n"/>
-      <c r="B5" s="74">
-        <f>input!B17</f>
-        <v/>
-      </c>
-      <c r="C5" s="55">
-        <f>IF(B5="","", "Cálculo")</f>
-        <v/>
-      </c>
-      <c r="D5" s="75">
-        <f>input!D17</f>
-        <v/>
-      </c>
-      <c r="E5" s="76">
-        <f t="array" ref="E5">IFERROR(INDEX(do_not_change__calculation_memo!$I$4:$I$17,MATCH(1,(do_not_change__calculation_memo!$B$4:$B$17=B5)*(do_not_change__calculation_memo!$C$4:$C$17="Venda"),0)),"")</f>
-        <v/>
-      </c>
-      <c r="F5" s="76">
-        <f>input!G17</f>
-        <v/>
-      </c>
-      <c r="G5" s="76">
-        <f>IFERROR(IF(B5="","",D5*F5-D5*E5),0)</f>
-        <v/>
-      </c>
+      <c r="B5" s="74" t="n"/>
+      <c r="C5" s="55" t="n"/>
+      <c r="D5" s="75" t="n"/>
+      <c r="E5" s="76" t="n"/>
+      <c r="F5" s="76" t="n"/>
+      <c r="G5" s="76" t="n"/>
       <c r="H5" s="77" t="n"/>
       <c r="I5" s="1" t="n"/>
       <c r="J5" s="1" t="n"/>
@@ -38435,30 +39142,12 @@
     </row>
     <row r="6" ht="12.75" customHeight="1" s="85">
       <c r="A6" s="1" t="n"/>
-      <c r="B6" s="74">
-        <f>input!B18</f>
-        <v/>
-      </c>
-      <c r="C6" s="55">
-        <f>IF(B6="","", "Cálculo")</f>
-        <v/>
-      </c>
-      <c r="D6" s="75">
-        <f>input!D18</f>
-        <v/>
-      </c>
-      <c r="E6" s="76">
-        <f t="array" ref="E6">IFERROR(INDEX(do_not_change__calculation_memo!$I$4:$I$17,MATCH(1,(do_not_change__calculation_memo!$B$4:$B$17=B6)*(do_not_change__calculation_memo!$C$4:$C$17="Venda"),0)),"")</f>
-        <v/>
-      </c>
-      <c r="F6" s="76">
-        <f>input!G18</f>
-        <v/>
-      </c>
-      <c r="G6" s="76">
-        <f>IFERROR(IF(B6="","",D6*F6-D6*E6),0)</f>
-        <v/>
-      </c>
+      <c r="B6" s="74" t="n"/>
+      <c r="C6" s="55" t="n"/>
+      <c r="D6" s="75" t="n"/>
+      <c r="E6" s="76" t="n"/>
+      <c r="F6" s="76" t="n"/>
+      <c r="G6" s="76" t="n"/>
       <c r="H6" s="77" t="n"/>
       <c r="I6" s="1" t="n"/>
       <c r="J6" s="1" t="n"/>
@@ -38483,30 +39172,12 @@
     </row>
     <row r="7" ht="12.75" customHeight="1" s="85">
       <c r="A7" s="1" t="n"/>
-      <c r="B7" s="74">
-        <f>input!B19</f>
-        <v/>
-      </c>
-      <c r="C7" s="55">
-        <f>IF(B7="","", "Cálculo")</f>
-        <v/>
-      </c>
-      <c r="D7" s="75">
-        <f>input!D19</f>
-        <v/>
-      </c>
-      <c r="E7" s="76">
-        <f t="array" ref="E7">IFERROR(INDEX(do_not_change__calculation_memo!$I$4:$I$17,MATCH(1,(do_not_change__calculation_memo!$B$4:$B$17=B7)*(do_not_change__calculation_memo!$C$4:$C$17="Venda"),0)),"")</f>
-        <v/>
-      </c>
-      <c r="F7" s="76">
-        <f>input!G19</f>
-        <v/>
-      </c>
-      <c r="G7" s="76">
-        <f>IFERROR(IF(B7="","",D7*F7-D7*E7),0)</f>
-        <v/>
-      </c>
+      <c r="B7" s="74" t="n"/>
+      <c r="C7" s="55" t="n"/>
+      <c r="D7" s="75" t="n"/>
+      <c r="E7" s="76" t="n"/>
+      <c r="F7" s="76" t="n"/>
+      <c r="G7" s="76" t="n"/>
       <c r="H7" s="77" t="n"/>
       <c r="I7" s="1" t="n"/>
       <c r="J7" s="1" t="n"/>
@@ -38531,30 +39202,12 @@
     </row>
     <row r="8" ht="12.75" customHeight="1" s="85">
       <c r="A8" s="1" t="n"/>
-      <c r="B8" s="74">
-        <f>input!B20</f>
-        <v/>
-      </c>
-      <c r="C8" s="55">
-        <f>IF(B8="","", "Cálculo")</f>
-        <v/>
-      </c>
-      <c r="D8" s="75">
-        <f>input!D20</f>
-        <v/>
-      </c>
-      <c r="E8" s="76">
-        <f t="array" ref="E8">IFERROR(INDEX(do_not_change__calculation_memo!$I$4:$I$17,MATCH(1,(do_not_change__calculation_memo!$B$4:$B$17=B8)*(do_not_change__calculation_memo!$C$4:$C$17="Venda"),0)),"")</f>
-        <v/>
-      </c>
-      <c r="F8" s="76">
-        <f>input!G20</f>
-        <v/>
-      </c>
-      <c r="G8" s="76">
-        <f>IFERROR(IF(B8="","",D8*F8-D8*E8),0)</f>
-        <v/>
-      </c>
+      <c r="B8" s="74" t="n"/>
+      <c r="C8" s="55" t="n"/>
+      <c r="D8" s="75" t="n"/>
+      <c r="E8" s="76" t="n"/>
+      <c r="F8" s="76" t="n"/>
+      <c r="G8" s="76" t="n"/>
       <c r="H8" s="77" t="n"/>
       <c r="I8" s="1" t="n"/>
       <c r="J8" s="1" t="n"/>
@@ -38579,30 +39232,12 @@
     </row>
     <row r="9" ht="12.75" customHeight="1" s="85">
       <c r="A9" s="1" t="n"/>
-      <c r="B9" s="74">
-        <f>input!B21</f>
-        <v/>
-      </c>
-      <c r="C9" s="55">
-        <f>IF(B9="","", "Cálculo")</f>
-        <v/>
-      </c>
-      <c r="D9" s="75">
-        <f>input!D21</f>
-        <v/>
-      </c>
-      <c r="E9" s="76">
-        <f t="array" ref="E9">IFERROR(INDEX(do_not_change__calculation_memo!$I$4:$I$17,MATCH(1,(do_not_change__calculation_memo!$B$4:$B$17=B9)*(do_not_change__calculation_memo!$C$4:$C$17="Venda"),0)),"")</f>
-        <v/>
-      </c>
-      <c r="F9" s="76">
-        <f>input!G21</f>
-        <v/>
-      </c>
-      <c r="G9" s="76">
-        <f>IFERROR(IF(B9="","",D9*F9-D9*E9),0)</f>
-        <v/>
-      </c>
+      <c r="B9" s="74" t="n"/>
+      <c r="C9" s="55" t="n"/>
+      <c r="D9" s="75" t="n"/>
+      <c r="E9" s="76" t="n"/>
+      <c r="F9" s="76" t="n"/>
+      <c r="G9" s="76" t="n"/>
       <c r="H9" s="77" t="n"/>
       <c r="I9" s="1" t="n"/>
       <c r="J9" s="1" t="n"/>
@@ -38623,30 +39258,12 @@
     </row>
     <row r="10" ht="12.75" customHeight="1" s="85">
       <c r="A10" s="1" t="n"/>
-      <c r="B10" s="74">
-        <f>input!B22</f>
-        <v/>
-      </c>
-      <c r="C10" s="55">
-        <f>IF(B10="","", "Cálculo")</f>
-        <v/>
-      </c>
-      <c r="D10" s="75">
-        <f>input!D22</f>
-        <v/>
-      </c>
-      <c r="E10" s="76">
-        <f t="array" ref="E10">IFERROR(INDEX(do_not_change__calculation_memo!$I$4:$I$17,MATCH(1,(do_not_change__calculation_memo!$B$4:$B$17=B10)*(do_not_change__calculation_memo!$C$4:$C$17="Venda"),0)),"")</f>
-        <v/>
-      </c>
-      <c r="F10" s="76">
-        <f>input!G22</f>
-        <v/>
-      </c>
-      <c r="G10" s="76">
-        <f>IFERROR(IF(B10="","",D10*F10-D10*E10),0)</f>
-        <v/>
-      </c>
+      <c r="B10" s="74" t="n"/>
+      <c r="C10" s="55" t="n"/>
+      <c r="D10" s="75" t="n"/>
+      <c r="E10" s="76" t="n"/>
+      <c r="F10" s="76" t="n"/>
+      <c r="G10" s="76" t="n"/>
       <c r="H10" s="77" t="n"/>
       <c r="Z10" s="1" t="n"/>
       <c r="AA10" s="1" t="n"/>
@@ -38654,30 +39271,12 @@
     </row>
     <row r="11" ht="12.75" customHeight="1" s="85">
       <c r="A11" s="1" t="n"/>
-      <c r="B11" s="74">
-        <f>input!B23</f>
-        <v/>
-      </c>
-      <c r="C11" s="55">
-        <f>IF(B11="","", "Cálculo")</f>
-        <v/>
-      </c>
-      <c r="D11" s="75">
-        <f>input!D23</f>
-        <v/>
-      </c>
-      <c r="E11" s="76">
-        <f t="array" ref="E11">IFERROR(INDEX(do_not_change__calculation_memo!$I$4:$I$17,MATCH(1,(do_not_change__calculation_memo!$B$4:$B$17=B11)*(do_not_change__calculation_memo!$C$4:$C$17="Venda"),0)),"")</f>
-        <v/>
-      </c>
-      <c r="F11" s="76">
-        <f>input!G23</f>
-        <v/>
-      </c>
-      <c r="G11" s="76">
-        <f>IFERROR(IF(B11="","",D11*F11-D11*E11),0)</f>
-        <v/>
-      </c>
+      <c r="B11" s="74" t="n"/>
+      <c r="C11" s="55" t="n"/>
+      <c r="D11" s="75" t="n"/>
+      <c r="E11" s="76" t="n"/>
+      <c r="F11" s="76" t="n"/>
+      <c r="G11" s="76" t="n"/>
       <c r="H11" s="77" t="n"/>
       <c r="Z11" s="1" t="n"/>
       <c r="AA11" s="1" t="n"/>
@@ -38685,30 +39284,12 @@
     </row>
     <row r="12" ht="12.75" customHeight="1" s="85">
       <c r="A12" s="1" t="n"/>
-      <c r="B12" s="74">
-        <f>input!B24</f>
-        <v/>
-      </c>
-      <c r="C12" s="55">
-        <f>IF(B12="","", "Cálculo")</f>
-        <v/>
-      </c>
-      <c r="D12" s="75">
-        <f>input!D24</f>
-        <v/>
-      </c>
-      <c r="E12" s="76">
-        <f t="array" ref="E12">IFERROR(INDEX(do_not_change__calculation_memo!$I$4:$I$17,MATCH(1,(do_not_change__calculation_memo!$B$4:$B$17=B12)*(do_not_change__calculation_memo!$C$4:$C$17="Venda"),0)),"")</f>
-        <v/>
-      </c>
-      <c r="F12" s="76">
-        <f>input!G24</f>
-        <v/>
-      </c>
-      <c r="G12" s="76">
-        <f>IFERROR(IF(B12="","",D12*F12-D12*E12),0)</f>
-        <v/>
-      </c>
+      <c r="B12" s="74" t="n"/>
+      <c r="C12" s="55" t="n"/>
+      <c r="D12" s="75" t="n"/>
+      <c r="E12" s="76" t="n"/>
+      <c r="F12" s="76" t="n"/>
+      <c r="G12" s="76" t="n"/>
       <c r="H12" s="77" t="n"/>
       <c r="W12" s="1" t="n"/>
       <c r="X12" s="1" t="n"/>
@@ -38719,30 +39300,12 @@
     </row>
     <row r="13" ht="12.75" customHeight="1" s="85">
       <c r="A13" s="1" t="n"/>
-      <c r="B13" s="74">
-        <f>input!B25</f>
-        <v/>
-      </c>
-      <c r="C13" s="55">
-        <f>IF(B13="","", "Cálculo")</f>
-        <v/>
-      </c>
-      <c r="D13" s="75">
-        <f>input!D25</f>
-        <v/>
-      </c>
-      <c r="E13" s="76">
-        <f t="array" ref="E13">IFERROR(INDEX(do_not_change__calculation_memo!$I$4:$I$17,MATCH(1,(do_not_change__calculation_memo!$B$4:$B$17=B13)*(do_not_change__calculation_memo!$C$4:$C$17="Venda"),0)),"")</f>
-        <v/>
-      </c>
-      <c r="F13" s="76">
-        <f>input!G25</f>
-        <v/>
-      </c>
-      <c r="G13" s="76">
-        <f>IFERROR(IF(B13="","",D13*F13-D13*E13),0)</f>
-        <v/>
-      </c>
+      <c r="B13" s="74" t="n"/>
+      <c r="C13" s="55" t="n"/>
+      <c r="D13" s="75" t="n"/>
+      <c r="E13" s="76" t="n"/>
+      <c r="F13" s="76" t="n"/>
+      <c r="G13" s="76" t="n"/>
       <c r="H13" s="77" t="n"/>
       <c r="Z13" s="1" t="n"/>
       <c r="AA13" s="1" t="n"/>
@@ -38768,16 +39331,11 @@
           <t>Information for current declaration (2025) - Assets and Rights</t>
         </is>
       </c>
-      <c r="C15" s="86" t="n"/>
-      <c r="D15" s="86" t="n"/>
-      <c r="E15" s="86" t="n"/>
-      <c r="F15" s="86" t="n"/>
       <c r="G15" s="87" t="inlineStr">
         <is>
           <t>Detalhe no campo 'Discriminação'</t>
         </is>
       </c>
-      <c r="H15" s="88" t="n"/>
       <c r="I15" s="43" t="n"/>
       <c r="J15" s="43" t="n"/>
       <c r="K15" s="43" t="n"/>
@@ -38868,23 +39426,23 @@
         </is>
       </c>
       <c r="D17" s="81">
-        <f t="array" ref="D17">INDEX(do_not_change__calculation_memo!$N$4:$N$17,MATCH(B17,do_not_change__calculation_memo!$B$4:$B$17,1))</f>
+        <f>LOOKUP(2,1/(do_not_change__calculation_memo!$B$4:$B$43&lt;&gt;""),do_not_change__calculation_memo!$K$4:$K$43)</f>
         <v/>
       </c>
       <c r="E17" s="76">
-        <f>F17/D17</f>
+        <f>IFERROR(F17/D17,0)</f>
         <v/>
       </c>
       <c r="F17" s="76">
-        <f t="array" ref="F17">INDEX(do_not_change__calculation_memo!$R$4:$R$17,MATCH(B17,do_not_change__calculation_memo!$B$4:$B$17,1))</f>
+        <f>LOOKUP(2,1/(do_not_change__calculation_memo!$B$4:$B$43&lt;&gt;""),do_not_change__calculation_memo!$N$4:$N$43)</f>
         <v/>
       </c>
       <c r="G17" s="82">
-        <f>H17/D17</f>
+        <f>IFERROR(H17/D17,0)</f>
         <v/>
       </c>
       <c r="H17" s="82">
-        <f t="array" ref="H17">INDEX(do_not_change__calculation_memo!$V$4:$V$17,MATCH(B17,do_not_change__calculation_memo!$B$4:$B$17,1))</f>
+        <f>LOOKUP(2,1/(do_not_change__calculation_memo!$B$4:$B$43&lt;&gt;""),do_not_change__calculation_memo!$O$4:$O$43)</f>
         <v/>
       </c>
       <c r="W17" s="1" t="n"/>
@@ -38917,8 +39475,6 @@
           <t>Capital gain assessment (in case of sale)</t>
         </is>
       </c>
-      <c r="C19" s="86" t="n"/>
-      <c r="D19" s="88" t="n"/>
       <c r="E19" s="77" t="n"/>
       <c r="F19" s="77" t="n"/>
       <c r="G19" s="77" t="n"/>
@@ -38937,8 +39493,6 @@
           <t>total_profit_or_loss_brl</t>
         </is>
       </c>
-      <c r="C20" s="86" t="n"/>
-      <c r="D20" s="88" t="n"/>
       <c r="E20" s="77" t="n"/>
       <c r="F20" s="77" t="n"/>
       <c r="G20" s="77" t="n"/>
@@ -38953,11 +39507,9 @@
     <row r="21" ht="12.75" customHeight="1" s="85">
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="54">
-        <f>SUM($G$4:$G$13)</f>
-        <v/>
-      </c>
-      <c r="C21" s="86" t="n"/>
-      <c r="D21" s="88" t="n"/>
+        <f>SUM(do_not_change__calculation_memo!$P$4:$P$43)</f>
+        <v/>
+      </c>
       <c r="E21" s="77" t="n"/>
       <c r="F21" s="77" t="n"/>
       <c r="G21" s="77" t="n"/>
@@ -45693,15 +46245,6 @@
     <row r="999" ht="15.75" customHeight="1" s="85"/>
     <row r="1000" ht="15.75" customHeight="1" s="85"/>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="O9:R9"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B20:D20"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
